--- a/Scout/crk-vs-linn-mar-091826.xlsx
+++ b/Scout/crk-vs-linn-mar-091826.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rc841d88d22b94d4c"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R9201dd408cac46c6"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -115,6 +127,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>K DOT</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -130,6 +145,9 @@
     <t>Rush</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>TWINS WING</t>
   </si>
   <si>
@@ -157,12 +175,18 @@
     <t>D</t>
   </si>
   <si>
+    <t>I DOT UNDER</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
     <t>Punt Rec</t>
   </si>
   <si>
+    <t>G DOT</t>
+  </si>
+  <si>
     <t>ISO @ 3</t>
   </si>
   <si>
@@ -190,6 +214,9 @@
     <t>FAR</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>Penalty</t>
   </si>
   <si>
@@ -223,6 +250,9 @@
     <t>Y TRIPS OVER</t>
   </si>
   <si>
+    <t>G TUCK K</t>
+  </si>
+  <si>
     <t>WING</t>
   </si>
   <si>
@@ -259,12 +289,18 @@
     <t>SCISSORS</t>
   </si>
   <si>
+    <t>UNDER K</t>
+  </si>
+  <si>
     <t>TWINS OVER</t>
   </si>
   <si>
     <t>TWINS PRO</t>
   </si>
   <si>
+    <t>GUN STACK G</t>
+  </si>
+  <si>
     <t>FG Block</t>
   </si>
   <si>
@@ -280,6 +316,9 @@
     <t>ZONE READ</t>
   </si>
   <si>
+    <t>G I DOT UNDER</t>
+  </si>
+  <si>
     <t>SPLIT</t>
   </si>
   <si>
@@ -307,7 +346,13 @@
     <t>PRO WING</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>HB SCHUTE</t>
+  </si>
+  <si>
+    <t>GUN</t>
   </si>
   <si>
     <t>BAL</t>
@@ -317,7 +362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y161"/>
+  <dimension ref="A1:AC161"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -395,6 +440,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -404,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -415,7 +472,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -426,19 +483,19 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>-40</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -449,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -461,33 +518,36 @@
         <v>-30</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" t="s">
-        <v>36</v>
-      </c>
-      <c r="U5" t="s">
-        <v>34</v>
-      </c>
-      <c r="X5">
+        <v>37</v>
+      </c>
+      <c r="P5" t="s">
+        <v>38</v>
+      </c>
+      <c r="W5" t="s">
+        <v>39</v>
+      </c>
+      <c r="X5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -499,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -511,33 +571,36 @@
         <v>-30</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T6" t="s">
-        <v>40</v>
-      </c>
-      <c r="U6" t="s">
-        <v>41</v>
-      </c>
-      <c r="X6">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="W6" t="s">
+        <v>39</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -549,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -561,33 +624,36 @@
         <v>-30</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J7">
         <v>-8</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="R7" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" t="s">
         <v>44</v>
       </c>
-      <c r="U7" t="s">
-        <v>34</v>
-      </c>
-      <c r="X7">
+      <c r="W7" t="s">
+        <v>39</v>
+      </c>
+      <c r="X7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -599,7 +665,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -611,15 +677,15 @@
         <v>-22</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="X8">
+        <v>52</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -631,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -643,30 +709,33 @@
         <v>-29</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
         <v>37</v>
       </c>
-      <c r="I9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" t="s">
-        <v>35</v>
-      </c>
-      <c r="U9" t="s">
-        <v>34</v>
-      </c>
-      <c r="X9">
+      <c r="P9" t="s">
+        <v>54</v>
+      </c>
+      <c r="W9" t="s">
+        <v>39</v>
+      </c>
+      <c r="X9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -678,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -690,30 +759,33 @@
         <v>-33</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10" t="s">
         <v>37</v>
       </c>
-      <c r="I10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10">
-        <v>3</v>
-      </c>
-      <c r="K10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" t="s">
-        <v>41</v>
-      </c>
-      <c r="S10" t="s">
-        <v>35</v>
-      </c>
-      <c r="U10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X10">
+      <c r="P10" t="s">
+        <v>54</v>
+      </c>
+      <c r="W10" t="s">
+        <v>47</v>
+      </c>
+      <c r="X10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -725,7 +797,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -737,30 +809,33 @@
         <v>-36</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" t="s">
-        <v>41</v>
-      </c>
-      <c r="S11" t="s">
-        <v>35</v>
-      </c>
-      <c r="U11" t="s">
-        <v>34</v>
-      </c>
-      <c r="X11">
+        <v>55</v>
+      </c>
+      <c r="P11" t="s">
+        <v>54</v>
+      </c>
+      <c r="W11" t="s">
+        <v>47</v>
+      </c>
+      <c r="X11" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -772,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -784,15 +859,15 @@
         <v>-36</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>29</v>
-      </c>
-      <c r="X12">
+        <v>33</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -804,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -816,33 +891,36 @@
         <v>-24</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J13">
         <v>5</v>
       </c>
       <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="R13" t="s">
-        <v>34</v>
-      </c>
-      <c r="S13" t="s">
-        <v>35</v>
-      </c>
-      <c r="T13" t="s">
-        <v>50</v>
-      </c>
-      <c r="U13" t="s">
-        <v>41</v>
-      </c>
-      <c r="X13">
+        <v>55</v>
+      </c>
+      <c r="P13" t="s">
+        <v>57</v>
+      </c>
+      <c r="W13" t="s">
+        <v>39</v>
+      </c>
+      <c r="X13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB13">
         <v>2</v>
       </c>
     </row>
@@ -854,7 +932,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -866,33 +944,36 @@
         <v>-29</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J14">
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>48</v>
-      </c>
-      <c r="R14" t="s">
-        <v>41</v>
-      </c>
-      <c r="S14" t="s">
-        <v>35</v>
-      </c>
-      <c r="T14" t="s">
-        <v>50</v>
-      </c>
-      <c r="U14" t="s">
-        <v>41</v>
-      </c>
-      <c r="X14">
+        <v>55</v>
+      </c>
+      <c r="P14" t="s">
+        <v>57</v>
+      </c>
+      <c r="W14" t="s">
+        <v>47</v>
+      </c>
+      <c r="X14" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB14">
         <v>2</v>
       </c>
     </row>
@@ -904,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -916,36 +997,39 @@
         <v>-36</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
         <v>37</v>
       </c>
-      <c r="I15" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" t="s">
-        <v>41</v>
-      </c>
-      <c r="S15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T15" t="s">
-        <v>51</v>
-      </c>
-      <c r="U15" t="s">
-        <v>34</v>
-      </c>
-      <c r="V15" t="s">
-        <v>34</v>
-      </c>
-      <c r="X15">
+      <c r="P15" t="s">
+        <v>44</v>
+      </c>
+      <c r="W15" t="s">
+        <v>47</v>
+      </c>
+      <c r="X15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB15">
         <v>2</v>
       </c>
     </row>
@@ -957,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -969,33 +1053,36 @@
         <v>-39</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" t="s">
-        <v>34</v>
-      </c>
-      <c r="S16" t="s">
-        <v>35</v>
-      </c>
-      <c r="T16" t="s">
-        <v>50</v>
-      </c>
-      <c r="U16" t="s">
-        <v>41</v>
-      </c>
-      <c r="X16">
+        <v>37</v>
+      </c>
+      <c r="P16" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB16">
         <v>2</v>
       </c>
     </row>
@@ -1007,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1019,33 +1106,36 @@
         <v>-38</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J17">
         <v>62</v>
       </c>
       <c r="K17" t="s">
-        <v>48</v>
-      </c>
-      <c r="R17" t="s">
-        <v>34</v>
-      </c>
-      <c r="S17" t="s">
-        <v>53</v>
-      </c>
-      <c r="T17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U17" t="s">
-        <v>41</v>
-      </c>
-      <c r="X17">
+        <v>55</v>
+      </c>
+      <c r="P17" t="s">
+        <v>44</v>
+      </c>
+      <c r="W17" t="s">
+        <v>39</v>
+      </c>
+      <c r="X17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
     </row>
@@ -1057,21 +1147,21 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>56</v>
-      </c>
-      <c r="X18">
+        <v>64</v>
+      </c>
+      <c r="AB18">
         <v>2</v>
       </c>
     </row>
@@ -1083,19 +1173,19 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F19">
         <v>-40</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -1106,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1118,30 +1208,33 @@
         <v>49</v>
       </c>
       <c r="G20" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20" t="s">
-        <v>48</v>
-      </c>
-      <c r="R20" t="s">
-        <v>34</v>
-      </c>
-      <c r="S20" t="s">
-        <v>58</v>
-      </c>
-      <c r="U20" t="s">
-        <v>41</v>
-      </c>
-      <c r="X20">
+        <v>55</v>
+      </c>
+      <c r="P20" t="s">
+        <v>30</v>
+      </c>
+      <c r="W20" t="s">
+        <v>39</v>
+      </c>
+      <c r="X20" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1153,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1165,30 +1258,33 @@
         <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J21">
         <v>-7</v>
       </c>
       <c r="K21" t="s">
-        <v>48</v>
-      </c>
-      <c r="R21" t="s">
-        <v>34</v>
-      </c>
-      <c r="S21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U21" t="s">
-        <v>41</v>
-      </c>
-      <c r="X21">
+        <v>55</v>
+      </c>
+      <c r="P21" t="s">
+        <v>67</v>
+      </c>
+      <c r="W21" t="s">
+        <v>39</v>
+      </c>
+      <c r="X21" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1200,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1212,30 +1308,33 @@
         <v>-43</v>
       </c>
       <c r="G22" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J22">
         <v>-10</v>
       </c>
       <c r="K22" t="s">
-        <v>48</v>
-      </c>
-      <c r="R22" t="s">
-        <v>34</v>
-      </c>
-      <c r="S22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U22" t="s">
-        <v>41</v>
-      </c>
-      <c r="X22">
+        <v>55</v>
+      </c>
+      <c r="P22" t="s">
+        <v>67</v>
+      </c>
+      <c r="W22" t="s">
+        <v>39</v>
+      </c>
+      <c r="X22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1247,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1259,30 +1358,33 @@
         <v>-33</v>
       </c>
       <c r="G23" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J23">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>48</v>
-      </c>
-      <c r="R23" t="s">
-        <v>34</v>
-      </c>
-      <c r="S23" t="s">
-        <v>43</v>
-      </c>
-      <c r="U23" t="s">
-        <v>34</v>
-      </c>
-      <c r="X23">
+        <v>55</v>
+      </c>
+      <c r="P23" t="s">
+        <v>30</v>
+      </c>
+      <c r="W23" t="s">
+        <v>39</v>
+      </c>
+      <c r="X23" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1294,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -1306,15 +1408,15 @@
         <v>-37</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
-      </c>
-      <c r="X24">
+        <v>70</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1326,7 +1428,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1338,36 +1440,39 @@
         <v>-25</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J25">
         <v>4</v>
       </c>
       <c r="K25" t="s">
-        <v>48</v>
-      </c>
-      <c r="R25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S25" t="s">
-        <v>53</v>
-      </c>
-      <c r="T25" t="s">
-        <v>62</v>
-      </c>
-      <c r="U25" t="s">
-        <v>34</v>
-      </c>
-      <c r="V25" t="s">
-        <v>34</v>
-      </c>
-      <c r="X25">
+        <v>55</v>
+      </c>
+      <c r="P25" t="s">
+        <v>67</v>
+      </c>
+      <c r="W25" t="s">
+        <v>39</v>
+      </c>
+      <c r="X25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB25">
         <v>3</v>
       </c>
     </row>
@@ -1379,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1391,36 +1496,39 @@
         <v>-29</v>
       </c>
       <c r="G26" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J26">
         <v>23</v>
       </c>
       <c r="K26" t="s">
-        <v>48</v>
-      </c>
-      <c r="R26" t="s">
-        <v>41</v>
-      </c>
-      <c r="S26" t="s">
-        <v>53</v>
-      </c>
-      <c r="T26" t="s">
-        <v>63</v>
-      </c>
-      <c r="U26" t="s">
-        <v>41</v>
-      </c>
-      <c r="V26" t="s">
-        <v>41</v>
-      </c>
-      <c r="X26">
+        <v>55</v>
+      </c>
+      <c r="P26" t="s">
+        <v>67</v>
+      </c>
+      <c r="W26" t="s">
+        <v>47</v>
+      </c>
+      <c r="X26" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB26">
         <v>3</v>
       </c>
     </row>
@@ -1432,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1444,36 +1552,39 @@
         <v>48</v>
       </c>
       <c r="G27" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J27">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>48</v>
-      </c>
-      <c r="R27" t="s">
-        <v>34</v>
-      </c>
-      <c r="S27" t="s">
-        <v>53</v>
-      </c>
-      <c r="T27" t="s">
-        <v>64</v>
-      </c>
-      <c r="U27" t="s">
-        <v>41</v>
-      </c>
-      <c r="V27" t="s">
-        <v>34</v>
-      </c>
-      <c r="X27">
+        <v>55</v>
+      </c>
+      <c r="P27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W27" t="s">
+        <v>39</v>
+      </c>
+      <c r="X27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB27">
         <v>3</v>
       </c>
     </row>
@@ -1485,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1497,36 +1608,39 @@
         <v>44</v>
       </c>
       <c r="G28" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H28" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
         <v>37</v>
       </c>
-      <c r="I28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J28">
-        <v>2</v>
-      </c>
-      <c r="K28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" t="s">
-        <v>34</v>
-      </c>
-      <c r="S28" t="s">
-        <v>53</v>
-      </c>
-      <c r="T28" t="s">
-        <v>65</v>
-      </c>
-      <c r="U28" t="s">
-        <v>34</v>
-      </c>
-      <c r="V28" t="s">
-        <v>34</v>
-      </c>
-      <c r="X28">
+      <c r="P28" t="s">
+        <v>30</v>
+      </c>
+      <c r="W28" t="s">
+        <v>39</v>
+      </c>
+      <c r="X28" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB28">
         <v>3</v>
       </c>
     </row>
@@ -1538,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1550,36 +1664,39 @@
         <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J29">
         <v>11</v>
       </c>
       <c r="K29" t="s">
-        <v>48</v>
-      </c>
-      <c r="R29" t="s">
-        <v>34</v>
-      </c>
-      <c r="S29" t="s">
-        <v>43</v>
-      </c>
-      <c r="T29" t="s">
-        <v>64</v>
-      </c>
-      <c r="U29" t="s">
-        <v>34</v>
-      </c>
-      <c r="V29" t="s">
-        <v>41</v>
-      </c>
-      <c r="X29">
+        <v>55</v>
+      </c>
+      <c r="P29" t="s">
+        <v>67</v>
+      </c>
+      <c r="W29" t="s">
+        <v>39</v>
+      </c>
+      <c r="X29" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB29">
         <v>3</v>
       </c>
     </row>
@@ -1591,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1603,36 +1720,39 @@
         <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" t="s">
-        <v>41</v>
-      </c>
-      <c r="S30" t="s">
-        <v>53</v>
-      </c>
-      <c r="T30" t="s">
-        <v>65</v>
-      </c>
-      <c r="U30" t="s">
-        <v>34</v>
-      </c>
-      <c r="V30" t="s">
-        <v>34</v>
-      </c>
-      <c r="X30">
+        <v>37</v>
+      </c>
+      <c r="P30" t="s">
+        <v>67</v>
+      </c>
+      <c r="W30" t="s">
+        <v>47</v>
+      </c>
+      <c r="X30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB30">
         <v>3</v>
       </c>
     </row>
@@ -1644,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1656,36 +1776,39 @@
         <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J31">
         <v>-3</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
-      </c>
-      <c r="R31" t="s">
-        <v>41</v>
-      </c>
-      <c r="S31" t="s">
-        <v>53</v>
-      </c>
-      <c r="T31" t="s">
-        <v>62</v>
-      </c>
-      <c r="U31" t="s">
-        <v>41</v>
-      </c>
-      <c r="V31" t="s">
-        <v>41</v>
-      </c>
-      <c r="X31">
+        <v>37</v>
+      </c>
+      <c r="P31" t="s">
+        <v>67</v>
+      </c>
+      <c r="W31" t="s">
+        <v>47</v>
+      </c>
+      <c r="X31" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB31">
         <v>3</v>
       </c>
     </row>
@@ -1697,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1709,33 +1832,36 @@
         <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I32" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
-      </c>
-      <c r="R32" t="s">
-        <v>34</v>
-      </c>
-      <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32" t="s">
-        <v>66</v>
-      </c>
-      <c r="U32" t="s">
-        <v>41</v>
-      </c>
-      <c r="X32">
+        <v>37</v>
+      </c>
+      <c r="P32" t="s">
+        <v>44</v>
+      </c>
+      <c r="W32" t="s">
+        <v>39</v>
+      </c>
+      <c r="X32" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB32">
         <v>3</v>
       </c>
     </row>
@@ -1747,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>3</v>
@@ -1759,33 +1885,36 @@
         <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
-      </c>
-      <c r="R33" t="s">
-        <v>34</v>
-      </c>
-      <c r="S33" t="s">
-        <v>43</v>
-      </c>
-      <c r="T33" t="s">
-        <v>54</v>
-      </c>
-      <c r="U33" t="s">
-        <v>34</v>
-      </c>
-      <c r="X33">
+        <v>37</v>
+      </c>
+      <c r="P33" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" t="s">
+        <v>39</v>
+      </c>
+      <c r="X33" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -1797,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -1809,33 +1938,36 @@
         <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
-      </c>
-      <c r="R34" t="s">
-        <v>34</v>
-      </c>
-      <c r="S34" t="s">
-        <v>43</v>
-      </c>
-      <c r="T34" t="s">
-        <v>67</v>
-      </c>
-      <c r="U34" t="s">
-        <v>41</v>
-      </c>
-      <c r="X34">
+        <v>37</v>
+      </c>
+      <c r="P34" t="s">
+        <v>44</v>
+      </c>
+      <c r="W34" t="s">
+        <v>39</v>
+      </c>
+      <c r="X34" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -1847,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1859,18 +1991,18 @@
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>48</v>
-      </c>
-      <c r="X35">
+        <v>55</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -1882,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1894,30 +2026,33 @@
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I36" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J36">
         <v>8</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
-      </c>
-      <c r="R36" t="s">
-        <v>34</v>
-      </c>
-      <c r="S36" t="s">
-        <v>69</v>
-      </c>
-      <c r="U36" t="s">
-        <v>34</v>
-      </c>
-      <c r="X36">
+        <v>37</v>
+      </c>
+      <c r="P36" t="s">
+        <v>67</v>
+      </c>
+      <c r="W36" t="s">
+        <v>39</v>
+      </c>
+      <c r="X36" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -1929,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1941,18 +2076,18 @@
         <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I37" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>48</v>
-      </c>
-      <c r="X37">
+        <v>55</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -1964,7 +2099,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1976,30 +2111,33 @@
         <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I38" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
-      </c>
-      <c r="R38" t="s">
-        <v>41</v>
-      </c>
-      <c r="S38" t="s">
-        <v>70</v>
-      </c>
-      <c r="U38" t="s">
-        <v>41</v>
-      </c>
-      <c r="X38">
+        <v>55</v>
+      </c>
+      <c r="P38" t="s">
+        <v>79</v>
+      </c>
+      <c r="W38" t="s">
+        <v>47</v>
+      </c>
+      <c r="X38" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -2011,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -2023,30 +2161,30 @@
         <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H39" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J39">
         <v>11</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
-      </c>
-      <c r="R39" t="s">
-        <v>34</v>
-      </c>
-      <c r="S39" t="s">
-        <v>70</v>
-      </c>
-      <c r="U39" t="s">
-        <v>41</v>
-      </c>
-      <c r="X39">
+        <v>37</v>
+      </c>
+      <c r="W39" t="s">
+        <v>39</v>
+      </c>
+      <c r="X39" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2058,7 +2196,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2070,30 +2208,33 @@
         <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J40">
         <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
-      </c>
-      <c r="R40" t="s">
-        <v>34</v>
-      </c>
-      <c r="S40" t="s">
-        <v>35</v>
-      </c>
-      <c r="U40" t="s">
-        <v>41</v>
-      </c>
-      <c r="X40">
+        <v>55</v>
+      </c>
+      <c r="P40" t="s">
+        <v>54</v>
+      </c>
+      <c r="W40" t="s">
+        <v>39</v>
+      </c>
+      <c r="X40" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2105,7 +2246,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2117,30 +2258,33 @@
         <v>6</v>
       </c>
       <c r="G41" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I41" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J41">
         <v>-1</v>
       </c>
       <c r="K41" t="s">
-        <v>48</v>
-      </c>
-      <c r="R41" t="s">
-        <v>41</v>
-      </c>
-      <c r="S41" t="s">
-        <v>35</v>
-      </c>
-      <c r="U41" t="s">
-        <v>34</v>
-      </c>
-      <c r="X41">
+        <v>55</v>
+      </c>
+      <c r="P41" t="s">
+        <v>54</v>
+      </c>
+      <c r="W41" t="s">
+        <v>47</v>
+      </c>
+      <c r="X41" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2152,7 +2296,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D42">
         <v>3</v>
@@ -2164,30 +2308,33 @@
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H42" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J42">
         <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>33</v>
-      </c>
-      <c r="R42" t="s">
-        <v>34</v>
-      </c>
-      <c r="S42" t="s">
-        <v>35</v>
-      </c>
-      <c r="U42" t="s">
-        <v>34</v>
-      </c>
-      <c r="X42">
+        <v>37</v>
+      </c>
+      <c r="P42" t="s">
+        <v>54</v>
+      </c>
+      <c r="W42" t="s">
+        <v>39</v>
+      </c>
+      <c r="X42" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2199,21 +2346,21 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F43">
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s">
-        <v>56</v>
-      </c>
-      <c r="X43">
+        <v>64</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2225,19 +2372,19 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F44">
         <v>-40</v>
       </c>
       <c r="G44" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
@@ -2248,7 +2395,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2260,33 +2407,36 @@
         <v>-24</v>
       </c>
       <c r="G45" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J45">
         <v>-1</v>
       </c>
       <c r="K45" t="s">
-        <v>33</v>
-      </c>
-      <c r="R45" t="s">
-        <v>34</v>
-      </c>
-      <c r="S45" t="s">
-        <v>39</v>
-      </c>
-      <c r="T45" t="s">
-        <v>73</v>
-      </c>
-      <c r="U45" t="s">
-        <v>34</v>
-      </c>
-      <c r="X45">
+        <v>37</v>
+      </c>
+      <c r="P45" t="s">
+        <v>44</v>
+      </c>
+      <c r="W45" t="s">
+        <v>39</v>
+      </c>
+      <c r="X45" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB45">
         <v>4</v>
       </c>
     </row>
@@ -2298,7 +2448,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2310,33 +2460,36 @@
         <v>-23</v>
       </c>
       <c r="G46" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H46" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J46">
         <v>12</v>
       </c>
       <c r="K46" t="s">
-        <v>48</v>
-      </c>
-      <c r="R46" t="s">
-        <v>41</v>
-      </c>
-      <c r="S46" t="s">
-        <v>43</v>
-      </c>
-      <c r="T46" t="s">
-        <v>74</v>
-      </c>
-      <c r="U46" t="s">
-        <v>41</v>
-      </c>
-      <c r="X46">
+        <v>55</v>
+      </c>
+      <c r="P46" t="s">
+        <v>44</v>
+      </c>
+      <c r="W46" t="s">
+        <v>47</v>
+      </c>
+      <c r="X46" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -2348,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2360,33 +2513,36 @@
         <v>-35</v>
       </c>
       <c r="G47" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J47">
         <v>-3</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
-      </c>
-      <c r="R47" t="s">
-        <v>34</v>
-      </c>
-      <c r="S47" t="s">
-        <v>35</v>
-      </c>
-      <c r="T47" t="s">
-        <v>73</v>
-      </c>
-      <c r="U47" t="s">
-        <v>41</v>
-      </c>
-      <c r="X47">
+        <v>37</v>
+      </c>
+      <c r="P47" t="s">
+        <v>38</v>
+      </c>
+      <c r="W47" t="s">
+        <v>39</v>
+      </c>
+      <c r="X47" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB47">
         <v>4</v>
       </c>
     </row>
@@ -2398,7 +2554,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2410,33 +2566,36 @@
         <v>-32</v>
       </c>
       <c r="G48" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>33</v>
-      </c>
-      <c r="R48" t="s">
-        <v>34</v>
-      </c>
-      <c r="S48" t="s">
-        <v>53</v>
-      </c>
-      <c r="T48" t="s">
-        <v>67</v>
-      </c>
-      <c r="U48" t="s">
-        <v>41</v>
-      </c>
-      <c r="X48">
+        <v>37</v>
+      </c>
+      <c r="P48" t="s">
+        <v>44</v>
+      </c>
+      <c r="W48" t="s">
+        <v>39</v>
+      </c>
+      <c r="X48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB48">
         <v>4</v>
       </c>
     </row>
@@ -2448,7 +2607,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -2460,33 +2619,36 @@
         <v>-32</v>
       </c>
       <c r="G49" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
-      </c>
-      <c r="R49" t="s">
-        <v>34</v>
-      </c>
-      <c r="S49" t="s">
-        <v>43</v>
-      </c>
-      <c r="T49" t="s">
-        <v>66</v>
-      </c>
-      <c r="U49" t="s">
-        <v>41</v>
-      </c>
-      <c r="X49">
+        <v>37</v>
+      </c>
+      <c r="P49" t="s">
+        <v>44</v>
+      </c>
+      <c r="W49" t="s">
+        <v>39</v>
+      </c>
+      <c r="X49" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB49">
         <v>4</v>
       </c>
     </row>
@@ -2498,7 +2660,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2510,30 +2672,33 @@
         <v>48</v>
       </c>
       <c r="G50" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H50" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J50">
         <v>3</v>
       </c>
       <c r="K50" t="s">
-        <v>48</v>
-      </c>
-      <c r="R50" t="s">
-        <v>34</v>
-      </c>
-      <c r="S50" t="s">
-        <v>35</v>
-      </c>
-      <c r="U50" t="s">
-        <v>34</v>
-      </c>
-      <c r="X50">
+        <v>55</v>
+      </c>
+      <c r="P50" t="s">
+        <v>54</v>
+      </c>
+      <c r="W50" t="s">
+        <v>39</v>
+      </c>
+      <c r="X50" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB50">
         <v>4</v>
       </c>
     </row>
@@ -2545,7 +2710,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -2557,30 +2722,33 @@
         <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H51" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>48</v>
-      </c>
-      <c r="R51" t="s">
-        <v>41</v>
-      </c>
-      <c r="S51" t="s">
-        <v>35</v>
-      </c>
-      <c r="U51" t="s">
-        <v>41</v>
-      </c>
-      <c r="X51">
+        <v>55</v>
+      </c>
+      <c r="P51" t="s">
+        <v>54</v>
+      </c>
+      <c r="W51" t="s">
+        <v>47</v>
+      </c>
+      <c r="X51" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB51">
         <v>4</v>
       </c>
     </row>
@@ -2592,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -2604,30 +2772,33 @@
         <v>44</v>
       </c>
       <c r="G52" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H52" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>48</v>
-      </c>
-      <c r="R52" t="s">
-        <v>41</v>
-      </c>
-      <c r="S52" t="s">
-        <v>75</v>
-      </c>
-      <c r="U52" t="s">
-        <v>41</v>
-      </c>
-      <c r="X52">
+        <v>55</v>
+      </c>
+      <c r="P52" t="s">
+        <v>67</v>
+      </c>
+      <c r="W52" t="s">
+        <v>47</v>
+      </c>
+      <c r="X52" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB52">
         <v>4</v>
       </c>
     </row>
@@ -2639,7 +2810,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -2651,24 +2822,27 @@
         <v>44</v>
       </c>
       <c r="G53" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I53" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J53">
         <v>-5</v>
       </c>
       <c r="K53" t="s">
-        <v>48</v>
-      </c>
-      <c r="R53" t="s">
-        <v>41</v>
-      </c>
-      <c r="S53" t="s">
-        <v>58</v>
-      </c>
-      <c r="X53">
+        <v>55</v>
+      </c>
+      <c r="P53" t="s">
+        <v>67</v>
+      </c>
+      <c r="W53" t="s">
+        <v>47</v>
+      </c>
+      <c r="X53" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB53">
         <v>4</v>
       </c>
     </row>
@@ -2680,7 +2854,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -2692,15 +2866,15 @@
         <v>49</v>
       </c>
       <c r="G54" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H54" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I54" t="s">
-        <v>46</v>
-      </c>
-      <c r="X54">
+        <v>52</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -2712,7 +2886,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2724,33 +2898,36 @@
         <v>-36</v>
       </c>
       <c r="G55" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
         <v>37</v>
       </c>
-      <c r="I55" t="s">
-        <v>38</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="K55" t="s">
-        <v>33</v>
-      </c>
-      <c r="R55" t="s">
-        <v>34</v>
-      </c>
-      <c r="S55" t="s">
-        <v>76</v>
-      </c>
-      <c r="T55" t="s">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s">
-        <v>34</v>
-      </c>
-      <c r="X55">
+      <c r="P55" t="s">
+        <v>57</v>
+      </c>
+      <c r="W55" t="s">
+        <v>39</v>
+      </c>
+      <c r="X55" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB55">
         <v>5</v>
       </c>
     </row>
@@ -2762,7 +2939,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -2774,33 +2951,36 @@
         <v>-37</v>
       </c>
       <c r="G56" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
-      </c>
-      <c r="R56" t="s">
-        <v>34</v>
-      </c>
-      <c r="S56" t="s">
-        <v>53</v>
-      </c>
-      <c r="T56" t="s">
-        <v>78</v>
-      </c>
-      <c r="U56" t="s">
-        <v>34</v>
-      </c>
-      <c r="X56">
+        <v>37</v>
+      </c>
+      <c r="P56" t="s">
+        <v>44</v>
+      </c>
+      <c r="W56" t="s">
+        <v>39</v>
+      </c>
+      <c r="X56" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB56">
         <v>5</v>
       </c>
     </row>
@@ -2812,7 +2992,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -2824,33 +3004,36 @@
         <v>-37</v>
       </c>
       <c r="G57" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J57">
         <v>-4</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
-      </c>
-      <c r="R57" t="s">
-        <v>34</v>
-      </c>
-      <c r="S57" t="s">
-        <v>53</v>
-      </c>
-      <c r="T57" t="s">
-        <v>67</v>
-      </c>
-      <c r="U57" t="s">
-        <v>41</v>
-      </c>
-      <c r="X57">
+        <v>37</v>
+      </c>
+      <c r="P57" t="s">
+        <v>44</v>
+      </c>
+      <c r="W57" t="s">
+        <v>39</v>
+      </c>
+      <c r="X57" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB57">
         <v>5</v>
       </c>
     </row>
@@ -2862,7 +3045,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2874,15 +3057,15 @@
         <v>-33</v>
       </c>
       <c r="G58" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I58" t="s">
-        <v>46</v>
-      </c>
-      <c r="X58">
+        <v>52</v>
+      </c>
+      <c r="AB58">
         <v>5</v>
       </c>
     </row>
@@ -2894,7 +3077,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2906,30 +3089,33 @@
         <v>-26</v>
       </c>
       <c r="G59" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>48</v>
-      </c>
-      <c r="R59" t="s">
-        <v>41</v>
-      </c>
-      <c r="S59" t="s">
-        <v>79</v>
-      </c>
-      <c r="U59" t="s">
-        <v>41</v>
-      </c>
-      <c r="X59">
+        <v>55</v>
+      </c>
+      <c r="P59" t="s">
+        <v>67</v>
+      </c>
+      <c r="W59" t="s">
+        <v>47</v>
+      </c>
+      <c r="X59" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB59">
         <v>5</v>
       </c>
     </row>
@@ -2941,7 +3127,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -2953,30 +3139,33 @@
         <v>-26</v>
       </c>
       <c r="G60" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H60" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>48</v>
-      </c>
-      <c r="R60" t="s">
-        <v>41</v>
-      </c>
-      <c r="S60" t="s">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s">
-        <v>34</v>
-      </c>
-      <c r="X60">
+        <v>55</v>
+      </c>
+      <c r="P60" t="s">
+        <v>44</v>
+      </c>
+      <c r="W60" t="s">
+        <v>47</v>
+      </c>
+      <c r="X60" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB60">
         <v>5</v>
       </c>
     </row>
@@ -2988,7 +3177,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -3000,30 +3189,33 @@
         <v>-26</v>
       </c>
       <c r="G61" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J61">
         <v>-9</v>
       </c>
       <c r="K61" t="s">
-        <v>48</v>
-      </c>
-      <c r="R61" t="s">
-        <v>41</v>
-      </c>
-      <c r="S61" t="s">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s">
-        <v>41</v>
-      </c>
-      <c r="X61">
+        <v>55</v>
+      </c>
+      <c r="P61" t="s">
+        <v>67</v>
+      </c>
+      <c r="W61" t="s">
+        <v>47</v>
+      </c>
+      <c r="X61" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB61">
         <v>5</v>
       </c>
     </row>
@@ -3035,7 +3227,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -3047,15 +3239,15 @@
         <v>-17</v>
       </c>
       <c r="G62" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I62" t="s">
-        <v>29</v>
-      </c>
-      <c r="X62">
+        <v>33</v>
+      </c>
+      <c r="AB62">
         <v>5</v>
       </c>
     </row>
@@ -3067,7 +3259,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3079,33 +3271,36 @@
         <v>-43</v>
       </c>
       <c r="G63" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H63" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J63">
         <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>48</v>
-      </c>
-      <c r="R63" t="s">
-        <v>41</v>
-      </c>
-      <c r="S63" t="s">
-        <v>43</v>
-      </c>
-      <c r="T63" t="s">
-        <v>65</v>
-      </c>
-      <c r="U63" t="s">
-        <v>41</v>
-      </c>
-      <c r="X63">
+        <v>55</v>
+      </c>
+      <c r="P63" t="s">
+        <v>44</v>
+      </c>
+      <c r="W63" t="s">
+        <v>47</v>
+      </c>
+      <c r="X63" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB63">
         <v>6</v>
       </c>
     </row>
@@ -3117,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3129,33 +3324,36 @@
         <v>44</v>
       </c>
       <c r="G64" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J64">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>33</v>
-      </c>
-      <c r="R64" t="s">
+        <v>37</v>
+      </c>
+      <c r="P64" t="s">
+        <v>44</v>
+      </c>
+      <c r="W64" t="s">
+        <v>47</v>
+      </c>
+      <c r="X64" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y64" t="s">
         <v>41</v>
       </c>
-      <c r="S64" t="s">
-        <v>43</v>
-      </c>
-      <c r="T64" t="s">
-        <v>36</v>
-      </c>
-      <c r="U64" t="s">
-        <v>34</v>
-      </c>
-      <c r="X64">
+      <c r="Z64" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB64">
         <v>6</v>
       </c>
     </row>
@@ -3167,7 +3365,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3179,33 +3377,36 @@
         <v>43</v>
       </c>
       <c r="G65" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J65">
         <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>48</v>
-      </c>
-      <c r="R65" t="s">
+        <v>55</v>
+      </c>
+      <c r="P65" t="s">
+        <v>44</v>
+      </c>
+      <c r="W65" t="s">
+        <v>47</v>
+      </c>
+      <c r="X65" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y65" t="s">
         <v>41</v>
       </c>
-      <c r="S65" t="s">
-        <v>53</v>
-      </c>
-      <c r="T65" t="s">
-        <v>36</v>
-      </c>
-      <c r="U65" t="s">
-        <v>34</v>
-      </c>
-      <c r="X65">
+      <c r="Z65" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB65">
         <v>6</v>
       </c>
     </row>
@@ -3217,7 +3418,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -3229,33 +3430,36 @@
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H66" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J66">
         <v>5</v>
       </c>
       <c r="K66" t="s">
-        <v>48</v>
-      </c>
-      <c r="R66" t="s">
-        <v>41</v>
-      </c>
-      <c r="S66" t="s">
-        <v>35</v>
-      </c>
-      <c r="T66" t="s">
-        <v>77</v>
-      </c>
-      <c r="U66" t="s">
-        <v>34</v>
-      </c>
-      <c r="X66">
+        <v>55</v>
+      </c>
+      <c r="P66" t="s">
+        <v>57</v>
+      </c>
+      <c r="W66" t="s">
+        <v>47</v>
+      </c>
+      <c r="X66" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB66">
         <v>6</v>
       </c>
     </row>
@@ -3267,7 +3471,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3279,33 +3483,36 @@
         <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>33</v>
-      </c>
-      <c r="R67" t="s">
+        <v>37</v>
+      </c>
+      <c r="P67" t="s">
+        <v>44</v>
+      </c>
+      <c r="W67" t="s">
+        <v>47</v>
+      </c>
+      <c r="X67" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y67" t="s">
         <v>41</v>
       </c>
-      <c r="S67" t="s">
-        <v>53</v>
-      </c>
-      <c r="T67" t="s">
-        <v>36</v>
-      </c>
-      <c r="U67" t="s">
-        <v>34</v>
-      </c>
-      <c r="X67">
+      <c r="Z67" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB67">
         <v>6</v>
       </c>
     </row>
@@ -3317,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3329,33 +3536,36 @@
         <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H68" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68">
+        <v>4</v>
+      </c>
+      <c r="K68" t="s">
         <v>37</v>
       </c>
-      <c r="I68" t="s">
-        <v>38</v>
-      </c>
-      <c r="J68">
-        <v>4</v>
-      </c>
-      <c r="K68" t="s">
-        <v>33</v>
-      </c>
-      <c r="R68" t="s">
-        <v>41</v>
-      </c>
-      <c r="S68" t="s">
-        <v>43</v>
-      </c>
-      <c r="T68" t="s">
-        <v>65</v>
-      </c>
-      <c r="U68" t="s">
-        <v>34</v>
-      </c>
-      <c r="X68">
+      <c r="P68" t="s">
+        <v>44</v>
+      </c>
+      <c r="W68" t="s">
+        <v>47</v>
+      </c>
+      <c r="X68" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB68">
         <v>6</v>
       </c>
     </row>
@@ -3367,7 +3577,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -3379,18 +3589,18 @@
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I69" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
-      </c>
-      <c r="X69">
+        <v>37</v>
+      </c>
+      <c r="AB69">
         <v>6</v>
       </c>
     </row>
@@ -3402,7 +3612,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -3414,30 +3624,33 @@
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J70">
         <v>26</v>
       </c>
       <c r="K70" t="s">
-        <v>48</v>
-      </c>
-      <c r="R70" t="s">
-        <v>41</v>
-      </c>
-      <c r="T70" t="s">
-        <v>81</v>
-      </c>
-      <c r="U70" t="s">
-        <v>41</v>
-      </c>
-      <c r="X70">
+        <v>55</v>
+      </c>
+      <c r="P70" t="s">
+        <v>44</v>
+      </c>
+      <c r="W70" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB70">
         <v>6</v>
       </c>
     </row>
@@ -3449,21 +3662,21 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F71">
         <v>3</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>56</v>
-      </c>
-      <c r="X71">
+        <v>64</v>
+      </c>
+      <c r="AB71">
         <v>6</v>
       </c>
     </row>
@@ -3475,19 +3688,19 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F72">
         <v>-40</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I72" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73">
@@ -3498,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3510,30 +3723,33 @@
         <v>-20</v>
       </c>
       <c r="G73" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>48</v>
-      </c>
-      <c r="R73" t="s">
-        <v>41</v>
-      </c>
-      <c r="S73" t="s">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s">
-        <v>41</v>
-      </c>
-      <c r="X73">
+        <v>55</v>
+      </c>
+      <c r="P73" t="s">
+        <v>30</v>
+      </c>
+      <c r="W73" t="s">
+        <v>47</v>
+      </c>
+      <c r="X73" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB73">
         <v>7</v>
       </c>
     </row>
@@ -3545,7 +3761,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3557,27 +3773,30 @@
         <v>-20</v>
       </c>
       <c r="G74" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J74">
         <v>-1</v>
       </c>
       <c r="K74" t="s">
-        <v>48</v>
-      </c>
-      <c r="R74" t="s">
-        <v>41</v>
-      </c>
-      <c r="S74" t="s">
-        <v>79</v>
-      </c>
-      <c r="X74">
+        <v>55</v>
+      </c>
+      <c r="P74" t="s">
+        <v>92</v>
+      </c>
+      <c r="W74" t="s">
+        <v>47</v>
+      </c>
+      <c r="X74" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB74">
         <v>7</v>
       </c>
     </row>
@@ -3589,7 +3808,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -3601,13 +3820,13 @@
         <v>-40</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I75" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76">
@@ -3618,7 +3837,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3630,30 +3849,30 @@
         <v>-30</v>
       </c>
       <c r="G76" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J76">
         <v>7</v>
       </c>
       <c r="K76" t="s">
-        <v>33</v>
-      </c>
-      <c r="R76" t="s">
-        <v>41</v>
-      </c>
-      <c r="S76" t="s">
-        <v>82</v>
-      </c>
-      <c r="U76" t="s">
-        <v>41</v>
-      </c>
-      <c r="X76">
+        <v>37</v>
+      </c>
+      <c r="W76" t="s">
+        <v>47</v>
+      </c>
+      <c r="X76" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB76">
         <v>6</v>
       </c>
     </row>
@@ -3665,7 +3884,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D77">
         <v>2</v>
@@ -3677,30 +3896,33 @@
         <v>-37</v>
       </c>
       <c r="G77" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J77">
         <v>14</v>
       </c>
       <c r="K77" t="s">
-        <v>33</v>
-      </c>
-      <c r="R77" t="s">
-        <v>41</v>
-      </c>
-      <c r="S77" t="s">
-        <v>35</v>
-      </c>
-      <c r="U77" t="s">
-        <v>41</v>
-      </c>
-      <c r="X77">
+        <v>37</v>
+      </c>
+      <c r="P77" t="s">
+        <v>54</v>
+      </c>
+      <c r="W77" t="s">
+        <v>47</v>
+      </c>
+      <c r="X77" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB77">
         <v>6</v>
       </c>
     </row>
@@ -3712,7 +3934,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3724,30 +3946,33 @@
         <v>49</v>
       </c>
       <c r="G78" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H78" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J78">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>48</v>
-      </c>
-      <c r="R78" t="s">
-        <v>34</v>
-      </c>
-      <c r="S78" t="s">
-        <v>35</v>
-      </c>
-      <c r="U78" t="s">
-        <v>41</v>
-      </c>
-      <c r="X78">
+        <v>55</v>
+      </c>
+      <c r="P78" t="s">
+        <v>54</v>
+      </c>
+      <c r="W78" t="s">
+        <v>39</v>
+      </c>
+      <c r="X78" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB78">
         <v>6</v>
       </c>
     </row>
@@ -3759,7 +3984,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -3771,30 +3996,33 @@
         <v>48</v>
       </c>
       <c r="G79" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J79">
         <v>8</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
-      </c>
-      <c r="R79" t="s">
-        <v>34</v>
-      </c>
-      <c r="S79" t="s">
-        <v>75</v>
-      </c>
-      <c r="U79" t="s">
-        <v>34</v>
-      </c>
-      <c r="X79">
+        <v>37</v>
+      </c>
+      <c r="P79" t="s">
+        <v>67</v>
+      </c>
+      <c r="W79" t="s">
+        <v>39</v>
+      </c>
+      <c r="X79" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB79">
         <v>6</v>
       </c>
     </row>
@@ -3806,7 +4034,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -3818,24 +4046,27 @@
         <v>40</v>
       </c>
       <c r="G80" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I80" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J80">
         <v>6</v>
       </c>
       <c r="K80" t="s">
-        <v>33</v>
-      </c>
-      <c r="R80" t="s">
-        <v>34</v>
-      </c>
-      <c r="S80" t="s">
-        <v>35</v>
-      </c>
-      <c r="X80">
+        <v>37</v>
+      </c>
+      <c r="P80" t="s">
+        <v>54</v>
+      </c>
+      <c r="W80" t="s">
+        <v>39</v>
+      </c>
+      <c r="X80" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB80">
         <v>6</v>
       </c>
     </row>
@@ -3847,7 +4078,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3859,30 +4090,33 @@
         <v>34</v>
       </c>
       <c r="G81" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H81" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J81">
         <v>5</v>
       </c>
       <c r="K81" t="s">
-        <v>33</v>
-      </c>
-      <c r="R81" t="s">
-        <v>41</v>
-      </c>
-      <c r="S81" t="s">
-        <v>83</v>
-      </c>
-      <c r="U81" t="s">
-        <v>41</v>
-      </c>
-      <c r="X81">
+        <v>37</v>
+      </c>
+      <c r="P81" t="s">
+        <v>79</v>
+      </c>
+      <c r="W81" t="s">
+        <v>47</v>
+      </c>
+      <c r="X81" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB81">
         <v>6</v>
       </c>
     </row>
@@ -3894,7 +4128,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -3906,30 +4140,33 @@
         <v>29</v>
       </c>
       <c r="G82" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J82">
         <v>16</v>
       </c>
       <c r="K82" t="s">
-        <v>33</v>
-      </c>
-      <c r="R82" t="s">
-        <v>34</v>
-      </c>
-      <c r="S82" t="s">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s">
-        <v>34</v>
-      </c>
-      <c r="X82">
+        <v>37</v>
+      </c>
+      <c r="P82" t="s">
+        <v>95</v>
+      </c>
+      <c r="W82" t="s">
+        <v>39</v>
+      </c>
+      <c r="X82" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB82">
         <v>6</v>
       </c>
     </row>
@@ -3941,7 +4178,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3953,30 +4190,33 @@
         <v>13</v>
       </c>
       <c r="G83" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J83">
         <v>6</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
-      </c>
-      <c r="R83" t="s">
-        <v>41</v>
-      </c>
-      <c r="S83" t="s">
-        <v>75</v>
-      </c>
-      <c r="U83" t="s">
-        <v>41</v>
-      </c>
-      <c r="X83">
+        <v>37</v>
+      </c>
+      <c r="P83" t="s">
+        <v>67</v>
+      </c>
+      <c r="W83" t="s">
+        <v>47</v>
+      </c>
+      <c r="X83" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB83">
         <v>6</v>
       </c>
     </row>
@@ -3988,7 +4228,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4000,30 +4240,33 @@
         <v>7</v>
       </c>
       <c r="G84" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J84">
         <v>-8</v>
       </c>
       <c r="K84" t="s">
-        <v>48</v>
-      </c>
-      <c r="R84" t="s">
-        <v>34</v>
-      </c>
-      <c r="S84" t="s">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s">
-        <v>34</v>
-      </c>
-      <c r="X84">
+        <v>55</v>
+      </c>
+      <c r="P84" t="s">
+        <v>95</v>
+      </c>
+      <c r="W84" t="s">
+        <v>39</v>
+      </c>
+      <c r="X84" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB84">
         <v>6</v>
       </c>
     </row>
@@ -4035,7 +4278,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -4047,30 +4290,33 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H85" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J85">
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>48</v>
-      </c>
-      <c r="R85" t="s">
-        <v>41</v>
-      </c>
-      <c r="S85" t="s">
-        <v>80</v>
-      </c>
-      <c r="U85" t="s">
-        <v>41</v>
-      </c>
-      <c r="X85">
+        <v>55</v>
+      </c>
+      <c r="P85" t="s">
+        <v>67</v>
+      </c>
+      <c r="W85" t="s">
+        <v>47</v>
+      </c>
+      <c r="X85" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB85">
         <v>6</v>
       </c>
     </row>
@@ -4082,7 +4328,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -4094,15 +4340,15 @@
         <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I86" t="s">
-        <v>85</v>
-      </c>
-      <c r="X86">
+        <v>97</v>
+      </c>
+      <c r="AB86">
         <v>6</v>
       </c>
     </row>
@@ -4114,19 +4360,19 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F87">
         <v>-40</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H87" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I87" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88">
@@ -4137,7 +4383,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4149,36 +4395,39 @@
         <v>-20</v>
       </c>
       <c r="G88" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H88" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J88">
         <v>7</v>
       </c>
       <c r="K88" t="s">
-        <v>48</v>
-      </c>
-      <c r="R88" t="s">
-        <v>34</v>
-      </c>
-      <c r="S88" t="s">
-        <v>53</v>
-      </c>
-      <c r="T88" t="s">
-        <v>87</v>
-      </c>
-      <c r="U88" t="s">
-        <v>41</v>
-      </c>
-      <c r="V88" t="s">
-        <v>41</v>
-      </c>
-      <c r="X88">
+        <v>55</v>
+      </c>
+      <c r="P88" t="s">
+        <v>30</v>
+      </c>
+      <c r="W88" t="s">
+        <v>39</v>
+      </c>
+      <c r="X88" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB88">
         <v>8</v>
       </c>
     </row>
@@ -4190,7 +4439,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4202,36 +4451,39 @@
         <v>-27</v>
       </c>
       <c r="G89" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H89" t="s">
+        <v>42</v>
+      </c>
+      <c r="I89" t="s">
+        <v>43</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89" t="s">
         <v>37</v>
       </c>
-      <c r="I89" t="s">
-        <v>38</v>
-      </c>
-      <c r="J89">
-        <v>1</v>
-      </c>
-      <c r="K89" t="s">
-        <v>33</v>
-      </c>
-      <c r="R89" t="s">
-        <v>34</v>
-      </c>
-      <c r="S89" t="s">
-        <v>53</v>
-      </c>
-      <c r="T89" t="s">
-        <v>88</v>
-      </c>
-      <c r="U89" t="s">
-        <v>34</v>
-      </c>
-      <c r="V89" t="s">
-        <v>34</v>
-      </c>
-      <c r="X89">
+      <c r="P89" t="s">
+        <v>30</v>
+      </c>
+      <c r="W89" t="s">
+        <v>39</v>
+      </c>
+      <c r="X89" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB89">
         <v>8</v>
       </c>
     </row>
@@ -4243,7 +4495,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -4255,33 +4507,36 @@
         <v>-28</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H90" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>48</v>
-      </c>
-      <c r="R90" t="s">
-        <v>34</v>
-      </c>
-      <c r="S90" t="s">
-        <v>89</v>
-      </c>
-      <c r="T90" t="s">
-        <v>90</v>
-      </c>
-      <c r="U90" t="s">
-        <v>41</v>
-      </c>
-      <c r="X90">
+        <v>55</v>
+      </c>
+      <c r="P90" t="s">
+        <v>101</v>
+      </c>
+      <c r="W90" t="s">
+        <v>39</v>
+      </c>
+      <c r="X90" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB90">
         <v>8</v>
       </c>
     </row>
@@ -4293,7 +4548,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4305,36 +4560,39 @@
         <v>-31</v>
       </c>
       <c r="G91" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H91" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J91">
         <v>-2</v>
       </c>
       <c r="K91" t="s">
-        <v>33</v>
-      </c>
-      <c r="R91" t="s">
-        <v>34</v>
-      </c>
-      <c r="S91" t="s">
-        <v>53</v>
-      </c>
-      <c r="T91" t="s">
-        <v>62</v>
-      </c>
-      <c r="U91" t="s">
-        <v>34</v>
-      </c>
-      <c r="V91" t="s">
-        <v>34</v>
-      </c>
-      <c r="X91">
+        <v>37</v>
+      </c>
+      <c r="P91" t="s">
+        <v>67</v>
+      </c>
+      <c r="W91" t="s">
+        <v>39</v>
+      </c>
+      <c r="X91" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB91">
         <v>8</v>
       </c>
     </row>
@@ -4346,7 +4604,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4358,33 +4616,36 @@
         <v>-29</v>
       </c>
       <c r="G92" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J92">
         <v>11</v>
       </c>
       <c r="K92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R92" t="s">
+        <v>55</v>
+      </c>
+      <c r="P92" t="s">
+        <v>44</v>
+      </c>
+      <c r="W92" t="s">
+        <v>47</v>
+      </c>
+      <c r="X92" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y92" t="s">
         <v>41</v>
       </c>
-      <c r="S92" t="s">
-        <v>53</v>
-      </c>
-      <c r="T92" t="s">
-        <v>36</v>
-      </c>
-      <c r="U92" t="s">
-        <v>34</v>
-      </c>
-      <c r="X92">
+      <c r="Z92" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB92">
         <v>8</v>
       </c>
     </row>
@@ -4396,7 +4657,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -4408,33 +4669,36 @@
         <v>-40</v>
       </c>
       <c r="G93" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H93" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J93">
         <v>-3</v>
       </c>
       <c r="K93" t="s">
-        <v>33</v>
-      </c>
-      <c r="R93" t="s">
-        <v>34</v>
-      </c>
-      <c r="S93" t="s">
-        <v>35</v>
-      </c>
-      <c r="T93" t="s">
-        <v>91</v>
-      </c>
-      <c r="U93" t="s">
-        <v>34</v>
-      </c>
-      <c r="X93">
+        <v>37</v>
+      </c>
+      <c r="P93" t="s">
+        <v>57</v>
+      </c>
+      <c r="W93" t="s">
+        <v>39</v>
+      </c>
+      <c r="X93" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB93">
         <v>8</v>
       </c>
     </row>
@@ -4446,7 +4710,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D94">
         <v>4</v>
@@ -4458,15 +4722,15 @@
         <v>-37</v>
       </c>
       <c r="G94" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H94" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I94" t="s">
-        <v>92</v>
-      </c>
-      <c r="X94">
+        <v>105</v>
+      </c>
+      <c r="AB94">
         <v>8</v>
       </c>
     </row>
@@ -4478,7 +4742,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4490,24 +4754,27 @@
         <v>-7</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I95" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J95">
         <v>-3</v>
       </c>
       <c r="K95" t="s">
-        <v>48</v>
-      </c>
-      <c r="R95" t="s">
-        <v>34</v>
-      </c>
-      <c r="S95" t="s">
-        <v>35</v>
-      </c>
-      <c r="X95">
+        <v>55</v>
+      </c>
+      <c r="P95" t="s">
+        <v>54</v>
+      </c>
+      <c r="W95" t="s">
+        <v>39</v>
+      </c>
+      <c r="X95" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB95">
         <v>7</v>
       </c>
     </row>
@@ -4519,7 +4786,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4531,30 +4798,33 @@
         <v>-4</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J96">
         <v>4</v>
       </c>
       <c r="K96" t="s">
-        <v>48</v>
-      </c>
-      <c r="R96" t="s">
-        <v>34</v>
-      </c>
-      <c r="S96" t="s">
-        <v>35</v>
-      </c>
-      <c r="U96" t="s">
-        <v>34</v>
-      </c>
-      <c r="X96">
+        <v>55</v>
+      </c>
+      <c r="P96" t="s">
+        <v>54</v>
+      </c>
+      <c r="W96" t="s">
+        <v>39</v>
+      </c>
+      <c r="X96" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB96">
         <v>7</v>
       </c>
     </row>
@@ -4566,7 +4836,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -4578,30 +4848,33 @@
         <v>-8</v>
       </c>
       <c r="G97" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>48</v>
-      </c>
-      <c r="R97" t="s">
-        <v>34</v>
-      </c>
-      <c r="S97" t="s">
-        <v>35</v>
-      </c>
-      <c r="U97" t="s">
-        <v>41</v>
-      </c>
-      <c r="X97">
+        <v>55</v>
+      </c>
+      <c r="P97" t="s">
+        <v>54</v>
+      </c>
+      <c r="W97" t="s">
+        <v>39</v>
+      </c>
+      <c r="X97" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB97">
         <v>7</v>
       </c>
     </row>
@@ -4613,7 +4886,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D98">
         <v>3</v>
@@ -4625,30 +4898,33 @@
         <v>-8</v>
       </c>
       <c r="G98" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J98">
         <v>13</v>
       </c>
       <c r="K98" t="s">
-        <v>33</v>
-      </c>
-      <c r="R98" t="s">
-        <v>41</v>
-      </c>
-      <c r="S98" t="s">
-        <v>69</v>
-      </c>
-      <c r="U98" t="s">
-        <v>41</v>
-      </c>
-      <c r="X98">
+        <v>37</v>
+      </c>
+      <c r="P98" t="s">
+        <v>67</v>
+      </c>
+      <c r="W98" t="s">
+        <v>47</v>
+      </c>
+      <c r="X98" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB98">
         <v>7</v>
       </c>
     </row>
@@ -4660,7 +4936,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -4672,30 +4948,33 @@
         <v>-21</v>
       </c>
       <c r="G99" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s">
+        <v>42</v>
+      </c>
+      <c r="I99" t="s">
+        <v>43</v>
+      </c>
+      <c r="J99">
+        <v>4</v>
+      </c>
+      <c r="K99" t="s">
         <v>37</v>
       </c>
-      <c r="I99" t="s">
-        <v>38</v>
-      </c>
-      <c r="J99">
-        <v>4</v>
-      </c>
-      <c r="K99" t="s">
-        <v>33</v>
-      </c>
-      <c r="R99" t="s">
-        <v>34</v>
-      </c>
-      <c r="S99" t="s">
-        <v>35</v>
-      </c>
-      <c r="U99" t="s">
-        <v>34</v>
-      </c>
-      <c r="X99">
+      <c r="P99" t="s">
+        <v>95</v>
+      </c>
+      <c r="W99" t="s">
+        <v>39</v>
+      </c>
+      <c r="X99" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB99">
         <v>7</v>
       </c>
     </row>
@@ -4707,7 +4986,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -4719,33 +4998,33 @@
         <v>-25</v>
       </c>
       <c r="G100" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H100" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>48</v>
-      </c>
-      <c r="R100" t="s">
-        <v>34</v>
-      </c>
-      <c r="S100" t="s">
-        <v>83</v>
-      </c>
-      <c r="U100" t="s">
-        <v>41</v>
-      </c>
-      <c r="V100" t="s">
-        <v>41</v>
-      </c>
-      <c r="X100">
+        <v>55</v>
+      </c>
+      <c r="W100" t="s">
+        <v>39</v>
+      </c>
+      <c r="X100" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB100">
         <v>7</v>
       </c>
     </row>
@@ -4757,7 +5036,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D101">
         <v>3</v>
@@ -4769,30 +5048,33 @@
         <v>-25</v>
       </c>
       <c r="G101" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>48</v>
-      </c>
-      <c r="R101" t="s">
-        <v>41</v>
-      </c>
-      <c r="S101" t="s">
-        <v>69</v>
-      </c>
-      <c r="U101" t="s">
-        <v>41</v>
-      </c>
-      <c r="X101">
+        <v>55</v>
+      </c>
+      <c r="P101" t="s">
+        <v>67</v>
+      </c>
+      <c r="W101" t="s">
+        <v>47</v>
+      </c>
+      <c r="X101" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB101">
         <v>7</v>
       </c>
     </row>
@@ -4804,7 +5086,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D102">
         <v>4</v>
@@ -4816,15 +5098,15 @@
         <v>-25</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H102" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I102" t="s">
-        <v>59</v>
-      </c>
-      <c r="X102">
+        <v>68</v>
+      </c>
+      <c r="AB102">
         <v>7</v>
       </c>
     </row>
@@ -4836,7 +5118,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D103">
         <v>4</v>
@@ -4848,18 +5130,18 @@
         <v>-20</v>
       </c>
       <c r="G103" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H103" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I103" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
-      <c r="X103">
+      <c r="AB103">
         <v>7</v>
       </c>
     </row>
@@ -4871,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D104">
         <v>4</v>
@@ -4883,15 +5165,15 @@
         <v>-20</v>
       </c>
       <c r="G104" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H104" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I104" t="s">
-        <v>29</v>
-      </c>
-      <c r="X104">
+        <v>33</v>
+      </c>
+      <c r="AB104">
         <v>9</v>
       </c>
     </row>
@@ -4903,7 +5185,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -4915,33 +5197,36 @@
         <v>46</v>
       </c>
       <c r="G105" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H105" t="s">
+        <v>42</v>
+      </c>
+      <c r="I105" t="s">
+        <v>43</v>
+      </c>
+      <c r="J105">
+        <v>3</v>
+      </c>
+      <c r="K105" t="s">
         <v>37</v>
       </c>
-      <c r="I105" t="s">
-        <v>38</v>
-      </c>
-      <c r="J105">
-        <v>3</v>
-      </c>
-      <c r="K105" t="s">
-        <v>33</v>
-      </c>
-      <c r="R105" t="s">
-        <v>34</v>
-      </c>
-      <c r="S105" t="s">
-        <v>93</v>
-      </c>
-      <c r="T105" t="s">
-        <v>73</v>
-      </c>
-      <c r="U105" t="s">
-        <v>34</v>
-      </c>
-      <c r="X105">
+      <c r="P105" t="s">
+        <v>44</v>
+      </c>
+      <c r="W105" t="s">
+        <v>39</v>
+      </c>
+      <c r="X105" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -4953,7 +5238,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -4965,24 +5250,27 @@
         <v>43</v>
       </c>
       <c r="G106" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I106" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J106">
         <v>5</v>
       </c>
       <c r="K106" t="s">
-        <v>48</v>
-      </c>
-      <c r="R106" t="s">
-        <v>34</v>
-      </c>
-      <c r="S106" t="s">
-        <v>93</v>
-      </c>
-      <c r="X106">
+        <v>55</v>
+      </c>
+      <c r="P106" t="s">
+        <v>44</v>
+      </c>
+      <c r="W106" t="s">
+        <v>39</v>
+      </c>
+      <c r="X106" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -4994,7 +5282,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5006,36 +5294,39 @@
         <v>38</v>
       </c>
       <c r="G107" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H107" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I107" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J107">
         <v>5</v>
       </c>
       <c r="K107" t="s">
-        <v>48</v>
-      </c>
-      <c r="R107" t="s">
-        <v>34</v>
-      </c>
-      <c r="S107" t="s">
-        <v>93</v>
-      </c>
-      <c r="T107" t="s">
-        <v>51</v>
-      </c>
-      <c r="U107" t="s">
-        <v>34</v>
-      </c>
-      <c r="V107" t="s">
-        <v>34</v>
-      </c>
-      <c r="X107">
+        <v>55</v>
+      </c>
+      <c r="P107" t="s">
+        <v>44</v>
+      </c>
+      <c r="W107" t="s">
+        <v>39</v>
+      </c>
+      <c r="X107" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB107">
         <v>8</v>
       </c>
     </row>
@@ -5047,7 +5338,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5059,24 +5350,27 @@
         <v>33</v>
       </c>
       <c r="G108" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I108" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J108">
         <v>-5</v>
       </c>
       <c r="K108" t="s">
-        <v>33</v>
-      </c>
-      <c r="R108" t="s">
-        <v>34</v>
-      </c>
-      <c r="S108" t="s">
-        <v>93</v>
-      </c>
-      <c r="X108">
+        <v>37</v>
+      </c>
+      <c r="P108" t="s">
+        <v>44</v>
+      </c>
+      <c r="W108" t="s">
+        <v>39</v>
+      </c>
+      <c r="X108" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB108">
         <v>8</v>
       </c>
     </row>
@@ -5088,7 +5382,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -5100,33 +5394,36 @@
         <v>38</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I109" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J109">
         <v>23</v>
       </c>
       <c r="K109" t="s">
-        <v>48</v>
-      </c>
-      <c r="R109" t="s">
-        <v>34</v>
-      </c>
-      <c r="S109" t="s">
-        <v>76</v>
-      </c>
-      <c r="T109" t="s">
-        <v>94</v>
-      </c>
-      <c r="U109" t="s">
-        <v>34</v>
-      </c>
-      <c r="X109">
+        <v>55</v>
+      </c>
+      <c r="P109" t="s">
+        <v>57</v>
+      </c>
+      <c r="W109" t="s">
+        <v>39</v>
+      </c>
+      <c r="X109" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB109">
         <v>8</v>
       </c>
     </row>
@@ -5138,7 +5435,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5150,33 +5447,36 @@
         <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H110" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I110" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J110">
         <v>6</v>
       </c>
       <c r="K110" t="s">
-        <v>48</v>
-      </c>
-      <c r="R110" t="s">
-        <v>34</v>
-      </c>
-      <c r="S110" t="s">
-        <v>35</v>
-      </c>
-      <c r="T110" t="s">
-        <v>91</v>
-      </c>
-      <c r="U110" t="s">
-        <v>34</v>
-      </c>
-      <c r="X110">
+        <v>55</v>
+      </c>
+      <c r="P110" t="s">
+        <v>57</v>
+      </c>
+      <c r="W110" t="s">
+        <v>39</v>
+      </c>
+      <c r="X110" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB110">
         <v>8</v>
       </c>
     </row>
@@ -5188,7 +5488,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -5200,33 +5500,36 @@
         <v>9</v>
       </c>
       <c r="G111" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H111" t="s">
+        <v>42</v>
+      </c>
+      <c r="I111" t="s">
+        <v>108</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
         <v>37</v>
       </c>
-      <c r="I111" t="s">
-        <v>95</v>
-      </c>
-      <c r="J111">
-        <v>2</v>
-      </c>
-      <c r="K111" t="s">
-        <v>33</v>
-      </c>
-      <c r="R111" t="s">
-        <v>34</v>
-      </c>
-      <c r="S111" t="s">
-        <v>35</v>
-      </c>
-      <c r="T111" t="s">
-        <v>91</v>
-      </c>
-      <c r="U111" t="s">
-        <v>34</v>
-      </c>
-      <c r="X111">
+      <c r="P111" t="s">
+        <v>57</v>
+      </c>
+      <c r="W111" t="s">
+        <v>39</v>
+      </c>
+      <c r="X111" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB111">
         <v>8</v>
       </c>
     </row>
@@ -5238,7 +5541,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5250,24 +5553,27 @@
         <v>-1</v>
       </c>
       <c r="G112" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I112" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J112">
         <v>5</v>
       </c>
       <c r="K112" t="s">
-        <v>33</v>
-      </c>
-      <c r="R112" t="s">
-        <v>41</v>
-      </c>
-      <c r="S112" t="s">
-        <v>35</v>
-      </c>
-      <c r="X112">
+        <v>37</v>
+      </c>
+      <c r="P112" t="s">
+        <v>54</v>
+      </c>
+      <c r="W112" t="s">
+        <v>47</v>
+      </c>
+      <c r="X112" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112">
         <v>10</v>
       </c>
     </row>
@@ -5279,7 +5585,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -5291,30 +5597,33 @@
         <v>-6</v>
       </c>
       <c r="G113" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H113" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I113" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J113">
         <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>33</v>
-      </c>
-      <c r="R113" t="s">
-        <v>34</v>
-      </c>
-      <c r="S113" t="s">
-        <v>35</v>
-      </c>
-      <c r="U113" t="s">
-        <v>41</v>
-      </c>
-      <c r="X113">
+        <v>37</v>
+      </c>
+      <c r="P113" t="s">
+        <v>54</v>
+      </c>
+      <c r="W113" t="s">
+        <v>39</v>
+      </c>
+      <c r="X113" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB113">
         <v>10</v>
       </c>
     </row>
@@ -5326,7 +5635,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5338,30 +5647,33 @@
         <v>-23</v>
       </c>
       <c r="G114" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H114" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I114" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J114">
         <v>7</v>
       </c>
       <c r="K114" t="s">
-        <v>33</v>
-      </c>
-      <c r="R114" t="s">
-        <v>34</v>
-      </c>
-      <c r="S114" t="s">
-        <v>75</v>
-      </c>
-      <c r="U114" t="s">
-        <v>34</v>
-      </c>
-      <c r="X114">
+        <v>37</v>
+      </c>
+      <c r="P114" t="s">
+        <v>67</v>
+      </c>
+      <c r="W114" t="s">
+        <v>39</v>
+      </c>
+      <c r="X114" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB114">
         <v>10</v>
       </c>
     </row>
@@ -5373,7 +5685,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -5385,33 +5697,36 @@
         <v>-30</v>
       </c>
       <c r="G115" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H115" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I115" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J115">
         <v>14</v>
       </c>
       <c r="K115" t="s">
-        <v>33</v>
-      </c>
-      <c r="R115" t="s">
-        <v>34</v>
-      </c>
-      <c r="S115" t="s">
-        <v>75</v>
-      </c>
-      <c r="U115" t="s">
-        <v>34</v>
-      </c>
-      <c r="V115" t="s">
-        <v>41</v>
-      </c>
-      <c r="X115">
+        <v>37</v>
+      </c>
+      <c r="P115" t="s">
+        <v>30</v>
+      </c>
+      <c r="W115" t="s">
+        <v>39</v>
+      </c>
+      <c r="X115" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA115" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB115">
         <v>10</v>
       </c>
     </row>
@@ -5423,7 +5738,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -5435,33 +5750,36 @@
         <v>-44</v>
       </c>
       <c r="G116" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H116" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I116" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J116">
         <v>56</v>
       </c>
       <c r="K116" t="s">
-        <v>33</v>
-      </c>
-      <c r="R116" t="s">
-        <v>34</v>
-      </c>
-      <c r="S116" t="s">
-        <v>75</v>
-      </c>
-      <c r="U116" t="s">
-        <v>34</v>
-      </c>
-      <c r="V116" t="s">
-        <v>41</v>
-      </c>
-      <c r="X116">
+        <v>37</v>
+      </c>
+      <c r="P116" t="s">
+        <v>30</v>
+      </c>
+      <c r="W116" t="s">
+        <v>39</v>
+      </c>
+      <c r="X116" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB116">
         <v>10</v>
       </c>
     </row>
@@ -5473,21 +5791,21 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F117">
         <v>3</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I117" t="s">
-        <v>56</v>
-      </c>
-      <c r="X117">
+        <v>64</v>
+      </c>
+      <c r="AB117">
         <v>10</v>
       </c>
     </row>
@@ -5499,19 +5817,19 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F118">
         <v>45</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H118" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I118" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119">
@@ -5522,7 +5840,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -5534,33 +5852,36 @@
         <v>-20</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J119">
         <v>4</v>
       </c>
       <c r="K119" t="s">
-        <v>48</v>
-      </c>
-      <c r="R119" t="s">
-        <v>34</v>
-      </c>
-      <c r="S119" t="s">
-        <v>35</v>
-      </c>
-      <c r="T119" t="s">
-        <v>91</v>
-      </c>
-      <c r="U119" t="s">
-        <v>34</v>
-      </c>
-      <c r="X119">
+        <v>55</v>
+      </c>
+      <c r="P119" t="s">
+        <v>57</v>
+      </c>
+      <c r="W119" t="s">
+        <v>39</v>
+      </c>
+      <c r="X119" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB119">
         <v>9</v>
       </c>
     </row>
@@ -5572,7 +5893,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -5584,33 +5905,36 @@
         <v>-24</v>
       </c>
       <c r="G120" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I120" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J120">
         <v>13</v>
       </c>
       <c r="K120" t="s">
-        <v>48</v>
-      </c>
-      <c r="R120" t="s">
-        <v>34</v>
-      </c>
-      <c r="S120" t="s">
-        <v>76</v>
-      </c>
-      <c r="T120" t="s">
-        <v>94</v>
-      </c>
-      <c r="U120" t="s">
-        <v>34</v>
-      </c>
-      <c r="X120">
+        <v>55</v>
+      </c>
+      <c r="P120" t="s">
+        <v>57</v>
+      </c>
+      <c r="W120" t="s">
+        <v>39</v>
+      </c>
+      <c r="X120" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB120">
         <v>9</v>
       </c>
     </row>
@@ -5622,7 +5946,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -5634,33 +5958,36 @@
         <v>-37</v>
       </c>
       <c r="G121" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H121" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I121" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J121">
         <v>4</v>
       </c>
       <c r="K121" t="s">
-        <v>48</v>
-      </c>
-      <c r="R121" t="s">
-        <v>41</v>
-      </c>
-      <c r="S121" t="s">
-        <v>35</v>
-      </c>
-      <c r="T121" t="s">
-        <v>91</v>
-      </c>
-      <c r="U121" t="s">
-        <v>34</v>
-      </c>
-      <c r="X121">
+        <v>55</v>
+      </c>
+      <c r="P121" t="s">
+        <v>57</v>
+      </c>
+      <c r="W121" t="s">
+        <v>47</v>
+      </c>
+      <c r="X121" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB121">
         <v>9</v>
       </c>
     </row>
@@ -5672,7 +5999,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -5684,33 +6011,36 @@
         <v>-41</v>
       </c>
       <c r="G122" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>33</v>
-      </c>
-      <c r="R122" t="s">
+        <v>37</v>
+      </c>
+      <c r="P122" t="s">
+        <v>44</v>
+      </c>
+      <c r="W122" t="s">
+        <v>47</v>
+      </c>
+      <c r="X122" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y122" t="s">
         <v>41</v>
       </c>
-      <c r="S122" t="s">
-        <v>53</v>
-      </c>
-      <c r="T122" t="s">
-        <v>36</v>
-      </c>
-      <c r="U122" t="s">
-        <v>34</v>
-      </c>
-      <c r="X122">
+      <c r="Z122" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB122">
         <v>9</v>
       </c>
     </row>
@@ -5722,7 +6052,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -5734,18 +6064,18 @@
         <v>-41</v>
       </c>
       <c r="G123" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I123" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>33</v>
-      </c>
-      <c r="X123">
+        <v>37</v>
+      </c>
+      <c r="AB123">
         <v>9</v>
       </c>
     </row>
@@ -5757,7 +6087,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D124">
         <v>3</v>
@@ -5769,33 +6099,36 @@
         <v>-41</v>
       </c>
       <c r="G124" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I124" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J124">
         <v>7</v>
       </c>
       <c r="K124" t="s">
-        <v>48</v>
-      </c>
-      <c r="R124" t="s">
-        <v>41</v>
-      </c>
-      <c r="S124" t="s">
-        <v>43</v>
-      </c>
-      <c r="T124" t="s">
+        <v>55</v>
+      </c>
+      <c r="P124" t="s">
         <v>44</v>
       </c>
-      <c r="U124" t="s">
-        <v>41</v>
-      </c>
-      <c r="X124">
+      <c r="W124" t="s">
+        <v>47</v>
+      </c>
+      <c r="X124" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB124">
         <v>9</v>
       </c>
     </row>
@@ -5807,7 +6140,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -5819,33 +6152,36 @@
         <v>-48</v>
       </c>
       <c r="G125" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H125" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I125" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J125">
         <v>-10</v>
       </c>
       <c r="K125" t="s">
-        <v>33</v>
-      </c>
-      <c r="R125" t="s">
-        <v>34</v>
-      </c>
-      <c r="S125" t="s">
-        <v>35</v>
-      </c>
-      <c r="T125" t="s">
-        <v>91</v>
-      </c>
-      <c r="U125" t="s">
-        <v>34</v>
-      </c>
-      <c r="X125">
+        <v>37</v>
+      </c>
+      <c r="P125" t="s">
+        <v>57</v>
+      </c>
+      <c r="W125" t="s">
+        <v>39</v>
+      </c>
+      <c r="X125" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB125">
         <v>9</v>
       </c>
     </row>
@@ -5857,7 +6193,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -5869,33 +6205,36 @@
         <v>-38</v>
       </c>
       <c r="G126" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I126" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J126">
         <v>6</v>
       </c>
       <c r="K126" t="s">
-        <v>33</v>
-      </c>
-      <c r="R126" t="s">
-        <v>34</v>
-      </c>
-      <c r="S126" t="s">
-        <v>43</v>
-      </c>
-      <c r="T126" t="s">
-        <v>74</v>
-      </c>
-      <c r="U126" t="s">
-        <v>34</v>
-      </c>
-      <c r="X126">
+        <v>37</v>
+      </c>
+      <c r="P126" t="s">
+        <v>67</v>
+      </c>
+      <c r="W126" t="s">
+        <v>39</v>
+      </c>
+      <c r="X126" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB126">
         <v>9</v>
       </c>
     </row>
@@ -5907,7 +6246,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -5919,33 +6258,36 @@
         <v>-44</v>
       </c>
       <c r="G127" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H127" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I127" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J127">
         <v>8</v>
       </c>
       <c r="K127" t="s">
-        <v>48</v>
-      </c>
-      <c r="R127" t="s">
+        <v>55</v>
+      </c>
+      <c r="P127" t="s">
+        <v>44</v>
+      </c>
+      <c r="W127" t="s">
+        <v>47</v>
+      </c>
+      <c r="X127" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y127" t="s">
         <v>41</v>
       </c>
-      <c r="S127" t="s">
-        <v>53</v>
-      </c>
-      <c r="T127" t="s">
-        <v>36</v>
-      </c>
-      <c r="U127" t="s">
-        <v>34</v>
-      </c>
-      <c r="X127">
+      <c r="Z127" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB127">
         <v>9</v>
       </c>
     </row>
@@ -5957,7 +6299,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -5969,33 +6311,36 @@
         <v>48</v>
       </c>
       <c r="G128" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I128" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J128">
         <v>10</v>
       </c>
       <c r="K128" t="s">
-        <v>48</v>
-      </c>
-      <c r="R128" t="s">
-        <v>41</v>
-      </c>
-      <c r="S128" t="s">
-        <v>53</v>
-      </c>
-      <c r="T128" t="s">
-        <v>81</v>
-      </c>
-      <c r="U128" t="s">
-        <v>41</v>
-      </c>
-      <c r="X128">
+        <v>55</v>
+      </c>
+      <c r="P128" t="s">
+        <v>44</v>
+      </c>
+      <c r="W128" t="s">
+        <v>47</v>
+      </c>
+      <c r="X128" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB128">
         <v>9</v>
       </c>
     </row>
@@ -6007,7 +6352,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -6019,33 +6364,36 @@
         <v>38</v>
       </c>
       <c r="G129" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H129" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I129" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J129">
         <v>25</v>
       </c>
       <c r="K129" t="s">
-        <v>48</v>
-      </c>
-      <c r="R129" t="s">
-        <v>41</v>
-      </c>
-      <c r="S129" t="s">
-        <v>43</v>
-      </c>
-      <c r="T129" t="s">
-        <v>65</v>
-      </c>
-      <c r="U129" t="s">
-        <v>34</v>
-      </c>
-      <c r="X129">
+        <v>55</v>
+      </c>
+      <c r="P129" t="s">
+        <v>67</v>
+      </c>
+      <c r="W129" t="s">
+        <v>47</v>
+      </c>
+      <c r="X129" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB129">
         <v>9</v>
       </c>
     </row>
@@ -6057,7 +6405,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -6069,33 +6417,36 @@
         <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H130" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I130" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J130">
         <v>4</v>
       </c>
       <c r="K130" t="s">
-        <v>48</v>
-      </c>
-      <c r="R130" t="s">
-        <v>41</v>
-      </c>
-      <c r="S130" t="s">
-        <v>35</v>
-      </c>
-      <c r="T130" t="s">
-        <v>50</v>
-      </c>
-      <c r="U130" t="s">
-        <v>41</v>
-      </c>
-      <c r="X130">
+        <v>55</v>
+      </c>
+      <c r="P130" t="s">
+        <v>57</v>
+      </c>
+      <c r="W130" t="s">
+        <v>47</v>
+      </c>
+      <c r="X130" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB130">
         <v>9</v>
       </c>
     </row>
@@ -6107,7 +6458,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D131">
         <v>2</v>
@@ -6119,33 +6470,36 @@
         <v>9</v>
       </c>
       <c r="G131" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H131" t="s">
+        <v>42</v>
+      </c>
+      <c r="I131" t="s">
+        <v>43</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="K131" t="s">
         <v>37</v>
       </c>
-      <c r="I131" t="s">
-        <v>38</v>
-      </c>
-      <c r="J131">
-        <v>2</v>
-      </c>
-      <c r="K131" t="s">
-        <v>33</v>
-      </c>
-      <c r="R131" t="s">
-        <v>41</v>
-      </c>
-      <c r="S131" t="s">
-        <v>35</v>
-      </c>
-      <c r="T131" t="s">
-        <v>77</v>
-      </c>
-      <c r="U131" t="s">
-        <v>34</v>
-      </c>
-      <c r="X131">
+      <c r="P131" t="s">
+        <v>57</v>
+      </c>
+      <c r="W131" t="s">
+        <v>47</v>
+      </c>
+      <c r="X131" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB131">
         <v>9</v>
       </c>
     </row>
@@ -6157,7 +6511,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D132">
         <v>3</v>
@@ -6169,33 +6523,36 @@
         <v>7</v>
       </c>
       <c r="G132" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H132" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I132" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J132">
         <v>-4</v>
       </c>
       <c r="K132" t="s">
-        <v>33</v>
-      </c>
-      <c r="R132" t="s">
-        <v>41</v>
-      </c>
-      <c r="S132" t="s">
-        <v>35</v>
-      </c>
-      <c r="T132" t="s">
-        <v>91</v>
-      </c>
-      <c r="U132" t="s">
-        <v>34</v>
-      </c>
-      <c r="X132">
+        <v>37</v>
+      </c>
+      <c r="P132" t="s">
+        <v>57</v>
+      </c>
+      <c r="W132" t="s">
+        <v>47</v>
+      </c>
+      <c r="X132" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB132">
         <v>9</v>
       </c>
     </row>
@@ -6207,7 +6564,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D133">
         <v>4</v>
@@ -6219,33 +6576,36 @@
         <v>11</v>
       </c>
       <c r="G133" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I133" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="J133">
         <v>4</v>
       </c>
       <c r="K133" t="s">
-        <v>33</v>
-      </c>
-      <c r="R133" t="s">
-        <v>41</v>
-      </c>
-      <c r="S133" t="s">
-        <v>43</v>
-      </c>
-      <c r="T133" t="s">
+        <v>37</v>
+      </c>
+      <c r="P133" t="s">
         <v>44</v>
       </c>
-      <c r="U133" t="s">
-        <v>34</v>
-      </c>
-      <c r="X133">
+      <c r="W133" t="s">
+        <v>47</v>
+      </c>
+      <c r="X133" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB133">
         <v>9</v>
       </c>
     </row>
@@ -6257,7 +6617,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -6269,30 +6629,33 @@
         <v>-7</v>
       </c>
       <c r="G134" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H134" t="s">
+        <v>42</v>
+      </c>
+      <c r="I134" t="s">
+        <v>43</v>
+      </c>
+      <c r="J134">
+        <v>4</v>
+      </c>
+      <c r="K134" t="s">
         <v>37</v>
       </c>
-      <c r="I134" t="s">
-        <v>38</v>
-      </c>
-      <c r="J134">
-        <v>4</v>
-      </c>
-      <c r="K134" t="s">
-        <v>33</v>
-      </c>
-      <c r="R134" t="s">
-        <v>34</v>
-      </c>
-      <c r="S134" t="s">
-        <v>97</v>
-      </c>
-      <c r="U134" t="s">
-        <v>34</v>
-      </c>
-      <c r="X134">
+      <c r="P134" t="s">
+        <v>67</v>
+      </c>
+      <c r="W134" t="s">
+        <v>39</v>
+      </c>
+      <c r="X134" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB134">
         <v>11</v>
       </c>
     </row>
@@ -6304,7 +6667,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -6316,30 +6679,33 @@
         <v>-11</v>
       </c>
       <c r="G135" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H135" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I135" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J135">
         <v>5</v>
       </c>
       <c r="K135" t="s">
-        <v>33</v>
-      </c>
-      <c r="R135" t="s">
-        <v>34</v>
-      </c>
-      <c r="S135" t="s">
-        <v>75</v>
-      </c>
-      <c r="U135" t="s">
-        <v>34</v>
-      </c>
-      <c r="X135">
+        <v>37</v>
+      </c>
+      <c r="P135" t="s">
+        <v>30</v>
+      </c>
+      <c r="W135" t="s">
+        <v>39</v>
+      </c>
+      <c r="X135" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB135">
         <v>11</v>
       </c>
     </row>
@@ -6351,7 +6717,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D136">
         <v>3</v>
@@ -6363,30 +6729,33 @@
         <v>-16</v>
       </c>
       <c r="G136" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H136" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I136" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>48</v>
-      </c>
-      <c r="R136" t="s">
-        <v>34</v>
-      </c>
-      <c r="S136" t="s">
-        <v>75</v>
-      </c>
-      <c r="U136" t="s">
-        <v>34</v>
-      </c>
-      <c r="X136">
+        <v>55</v>
+      </c>
+      <c r="P136" t="s">
+        <v>111</v>
+      </c>
+      <c r="W136" t="s">
+        <v>39</v>
+      </c>
+      <c r="X136" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB136">
         <v>11</v>
       </c>
     </row>
@@ -6398,7 +6767,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D137">
         <v>4</v>
@@ -6410,15 +6779,15 @@
         <v>-16</v>
       </c>
       <c r="G137" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H137" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I137" t="s">
-        <v>46</v>
-      </c>
-      <c r="X137">
+        <v>52</v>
+      </c>
+      <c r="AB137">
         <v>11</v>
       </c>
     </row>
@@ -6430,7 +6799,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -6442,33 +6811,36 @@
         <v>40</v>
       </c>
       <c r="G138" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H138" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I138" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J138">
         <v>6</v>
       </c>
       <c r="K138" t="s">
-        <v>48</v>
-      </c>
-      <c r="R138" t="s">
-        <v>34</v>
-      </c>
-      <c r="S138" t="s">
-        <v>35</v>
-      </c>
-      <c r="T138" t="s">
-        <v>91</v>
-      </c>
-      <c r="U138" t="s">
-        <v>34</v>
-      </c>
-      <c r="X138">
+        <v>55</v>
+      </c>
+      <c r="P138" t="s">
+        <v>57</v>
+      </c>
+      <c r="W138" t="s">
+        <v>39</v>
+      </c>
+      <c r="X138" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB138">
         <v>10</v>
       </c>
     </row>
@@ -6480,7 +6852,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -6492,33 +6864,36 @@
         <v>34</v>
       </c>
       <c r="G139" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H139" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I139" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J139">
         <v>15</v>
       </c>
       <c r="K139" t="s">
-        <v>48</v>
-      </c>
-      <c r="R139" t="s">
-        <v>41</v>
-      </c>
-      <c r="S139" t="s">
-        <v>53</v>
-      </c>
-      <c r="T139" t="s">
-        <v>98</v>
-      </c>
-      <c r="U139" t="s">
-        <v>34</v>
-      </c>
-      <c r="X139">
+        <v>55</v>
+      </c>
+      <c r="P139" t="s">
+        <v>67</v>
+      </c>
+      <c r="W139" t="s">
+        <v>47</v>
+      </c>
+      <c r="X139" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB139">
         <v>10</v>
       </c>
     </row>
@@ -6530,7 +6905,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -6542,33 +6917,36 @@
         <v>19</v>
       </c>
       <c r="G140" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H140" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I140" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J140">
         <v>4</v>
       </c>
       <c r="K140" t="s">
-        <v>48</v>
-      </c>
-      <c r="R140" t="s">
-        <v>41</v>
-      </c>
-      <c r="S140" t="s">
-        <v>43</v>
-      </c>
-      <c r="T140" t="s">
-        <v>65</v>
-      </c>
-      <c r="U140" t="s">
-        <v>34</v>
-      </c>
-      <c r="X140">
+        <v>55</v>
+      </c>
+      <c r="P140" t="s">
+        <v>44</v>
+      </c>
+      <c r="W140" t="s">
+        <v>47</v>
+      </c>
+      <c r="X140" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB140">
         <v>10</v>
       </c>
     </row>
@@ -6580,7 +6958,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -6592,33 +6970,36 @@
         <v>15</v>
       </c>
       <c r="G141" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H141" t="s">
+        <v>42</v>
+      </c>
+      <c r="I141" t="s">
+        <v>43</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141" t="s">
         <v>37</v>
       </c>
-      <c r="I141" t="s">
+      <c r="P141" t="s">
         <v>38</v>
       </c>
-      <c r="J141">
-        <v>1</v>
-      </c>
-      <c r="K141" t="s">
-        <v>33</v>
-      </c>
-      <c r="R141" t="s">
-        <v>41</v>
-      </c>
-      <c r="S141" t="s">
-        <v>76</v>
-      </c>
-      <c r="T141" t="s">
-        <v>91</v>
-      </c>
-      <c r="U141" t="s">
-        <v>34</v>
-      </c>
-      <c r="X141">
+      <c r="W141" t="s">
+        <v>47</v>
+      </c>
+      <c r="X141" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB141">
         <v>10</v>
       </c>
     </row>
@@ -6630,7 +7011,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D142">
         <v>3</v>
@@ -6642,33 +7023,36 @@
         <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H142" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I142" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>33</v>
-      </c>
-      <c r="R142" t="s">
-        <v>41</v>
-      </c>
-      <c r="S142" t="s">
-        <v>43</v>
-      </c>
-      <c r="T142" t="s">
-        <v>67</v>
-      </c>
-      <c r="U142" t="s">
-        <v>34</v>
-      </c>
-      <c r="X142">
+        <v>37</v>
+      </c>
+      <c r="P142" t="s">
+        <v>44</v>
+      </c>
+      <c r="W142" t="s">
+        <v>47</v>
+      </c>
+      <c r="X142" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB142">
         <v>10</v>
       </c>
     </row>
@@ -6680,7 +7064,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D143">
         <v>4</v>
@@ -6692,33 +7076,36 @@
         <v>14</v>
       </c>
       <c r="G143" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H143" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I143" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J143">
         <v>7</v>
       </c>
       <c r="K143" t="s">
-        <v>48</v>
-      </c>
-      <c r="R143" t="s">
-        <v>41</v>
-      </c>
-      <c r="S143" t="s">
-        <v>53</v>
-      </c>
-      <c r="T143" t="s">
-        <v>81</v>
-      </c>
-      <c r="U143" t="s">
-        <v>41</v>
-      </c>
-      <c r="X143">
+        <v>55</v>
+      </c>
+      <c r="P143" t="s">
+        <v>44</v>
+      </c>
+      <c r="W143" t="s">
+        <v>47</v>
+      </c>
+      <c r="X143" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB143">
         <v>10</v>
       </c>
     </row>
@@ -6730,7 +7117,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -6742,36 +7129,39 @@
         <v>7</v>
       </c>
       <c r="G144" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H144" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I144" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J144">
         <v>6</v>
       </c>
       <c r="K144" t="s">
-        <v>48</v>
-      </c>
-      <c r="R144" t="s">
-        <v>41</v>
-      </c>
-      <c r="S144" t="s">
-        <v>53</v>
-      </c>
-      <c r="T144" t="s">
-        <v>64</v>
-      </c>
-      <c r="U144" t="s">
-        <v>34</v>
-      </c>
-      <c r="V144" t="s">
-        <v>41</v>
-      </c>
-      <c r="X144">
+        <v>55</v>
+      </c>
+      <c r="P144" t="s">
+        <v>67</v>
+      </c>
+      <c r="W144" t="s">
+        <v>47</v>
+      </c>
+      <c r="X144" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA144" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB144">
         <v>10</v>
       </c>
     </row>
@@ -6783,45 +7173,48 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
+        <v>34</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145" t="s">
+        <v>39</v>
+      </c>
+      <c r="H145" t="s">
+        <v>42</v>
+      </c>
+      <c r="I145" t="s">
+        <v>81</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145" t="s">
+        <v>55</v>
+      </c>
+      <c r="P145" t="s">
         <v>30</v>
       </c>
-      <c r="D145">
-        <v>2</v>
-      </c>
-      <c r="E145">
-        <v>1</v>
-      </c>
-      <c r="F145">
-        <v>1</v>
-      </c>
-      <c r="G145" t="s">
-        <v>34</v>
-      </c>
-      <c r="H145" t="s">
-        <v>37</v>
-      </c>
-      <c r="I145" t="s">
-        <v>71</v>
-      </c>
-      <c r="J145">
-        <v>1</v>
-      </c>
-      <c r="K145" t="s">
-        <v>48</v>
-      </c>
-      <c r="R145" t="s">
-        <v>41</v>
-      </c>
-      <c r="S145" t="s">
-        <v>43</v>
-      </c>
-      <c r="T145" t="s">
-        <v>87</v>
-      </c>
-      <c r="U145" t="s">
-        <v>34</v>
-      </c>
-      <c r="X145">
+      <c r="W145" t="s">
+        <v>47</v>
+      </c>
+      <c r="X145" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB145">
         <v>10</v>
       </c>
     </row>
@@ -6833,21 +7226,21 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F146">
         <v>3</v>
       </c>
       <c r="G146" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H146" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I146" t="s">
-        <v>56</v>
-      </c>
-      <c r="X146">
+        <v>64</v>
+      </c>
+      <c r="AB146">
         <v>10</v>
       </c>
     </row>
@@ -6859,19 +7252,19 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F147">
         <v>-40</v>
       </c>
       <c r="G147" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H147" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I147" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148">
@@ -6882,7 +7275,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -6894,30 +7287,33 @@
         <v>-12</v>
       </c>
       <c r="G148" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H148" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I148" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>48</v>
-      </c>
-      <c r="R148" t="s">
-        <v>34</v>
-      </c>
-      <c r="S148" t="s">
-        <v>43</v>
-      </c>
-      <c r="U148" t="s">
-        <v>41</v>
-      </c>
-      <c r="X148">
+        <v>55</v>
+      </c>
+      <c r="P148" t="s">
+        <v>30</v>
+      </c>
+      <c r="W148" t="s">
+        <v>39</v>
+      </c>
+      <c r="X148" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB148">
         <v>12</v>
       </c>
     </row>
@@ -6929,7 +7325,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D149">
         <v>2</v>
@@ -6941,30 +7337,33 @@
         <v>-12</v>
       </c>
       <c r="G149" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H149" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I149" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>48</v>
-      </c>
-      <c r="R149" t="s">
-        <v>34</v>
-      </c>
-      <c r="S149" t="s">
-        <v>43</v>
-      </c>
-      <c r="U149" t="s">
-        <v>34</v>
-      </c>
-      <c r="X149">
+        <v>55</v>
+      </c>
+      <c r="P149" t="s">
+        <v>67</v>
+      </c>
+      <c r="W149" t="s">
+        <v>39</v>
+      </c>
+      <c r="X149" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB149">
         <v>12</v>
       </c>
     </row>
@@ -6976,7 +7375,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -6988,30 +7387,33 @@
         <v>-12</v>
       </c>
       <c r="G150" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H150" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J150">
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>48</v>
-      </c>
-      <c r="R150" t="s">
-        <v>34</v>
-      </c>
-      <c r="S150" t="s">
-        <v>43</v>
-      </c>
-      <c r="U150" t="s">
-        <v>34</v>
-      </c>
-      <c r="X150">
+        <v>55</v>
+      </c>
+      <c r="P150" t="s">
+        <v>67</v>
+      </c>
+      <c r="W150" t="s">
+        <v>39</v>
+      </c>
+      <c r="X150" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB150">
         <v>12</v>
       </c>
     </row>
@@ -7023,7 +7425,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D151">
         <v>4</v>
@@ -7035,30 +7437,33 @@
         <v>-12</v>
       </c>
       <c r="G151" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H151" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I151" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J151">
         <v>40</v>
       </c>
       <c r="K151" t="s">
-        <v>33</v>
-      </c>
-      <c r="R151" t="s">
-        <v>34</v>
-      </c>
-      <c r="S151" t="s">
-        <v>43</v>
-      </c>
-      <c r="U151" t="s">
-        <v>34</v>
-      </c>
-      <c r="X151">
+        <v>37</v>
+      </c>
+      <c r="P151" t="s">
+        <v>67</v>
+      </c>
+      <c r="W151" t="s">
+        <v>39</v>
+      </c>
+      <c r="X151" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB151">
         <v>12</v>
       </c>
     </row>
@@ -7070,7 +7475,7 @@
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -7082,18 +7487,18 @@
         <v>48</v>
       </c>
       <c r="G152" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I152" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>48</v>
-      </c>
-      <c r="X152">
+        <v>55</v>
+      </c>
+      <c r="AB152">
         <v>12</v>
       </c>
     </row>
@@ -7105,7 +7510,7 @@
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -7117,30 +7522,33 @@
         <v>48</v>
       </c>
       <c r="G153" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H153" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I153" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J153">
         <v>12</v>
       </c>
       <c r="K153" t="s">
-        <v>33</v>
-      </c>
-      <c r="R153" t="s">
-        <v>41</v>
-      </c>
-      <c r="S153" t="s">
-        <v>43</v>
-      </c>
-      <c r="U153" t="s">
-        <v>41</v>
-      </c>
-      <c r="X153">
+        <v>37</v>
+      </c>
+      <c r="P153" t="s">
+        <v>30</v>
+      </c>
+      <c r="W153" t="s">
+        <v>47</v>
+      </c>
+      <c r="X153" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z153" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB153">
         <v>12</v>
       </c>
     </row>
@@ -7152,7 +7560,7 @@
         <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -7164,30 +7572,33 @@
         <v>36</v>
       </c>
       <c r="G154" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H154" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I154" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J154">
         <v>7</v>
       </c>
       <c r="K154" t="s">
-        <v>33</v>
-      </c>
-      <c r="R154" t="s">
-        <v>99</v>
-      </c>
-      <c r="S154" t="s">
-        <v>53</v>
-      </c>
-      <c r="U154" t="s">
-        <v>34</v>
-      </c>
-      <c r="X154">
+        <v>37</v>
+      </c>
+      <c r="P154" t="s">
+        <v>113</v>
+      </c>
+      <c r="W154" t="s">
+        <v>114</v>
+      </c>
+      <c r="X154" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB154">
         <v>12</v>
       </c>
     </row>
@@ -7199,7 +7610,7 @@
         <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D155">
         <v>2</v>
@@ -7211,30 +7622,33 @@
         <v>29</v>
       </c>
       <c r="G155" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H155" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I155" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J155">
         <v>2</v>
       </c>
       <c r="K155" t="s">
-        <v>33</v>
-      </c>
-      <c r="R155" t="s">
-        <v>41</v>
-      </c>
-      <c r="S155" t="s">
-        <v>43</v>
-      </c>
-      <c r="U155" t="s">
-        <v>41</v>
-      </c>
-      <c r="X155">
+        <v>37</v>
+      </c>
+      <c r="P155" t="s">
+        <v>30</v>
+      </c>
+      <c r="W155" t="s">
+        <v>47</v>
+      </c>
+      <c r="X155" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB155">
         <v>12</v>
       </c>
     </row>
@@ -7246,7 +7660,7 @@
         <v>4</v>
       </c>
       <c r="C156" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D156">
         <v>3</v>
@@ -7258,30 +7672,33 @@
         <v>27</v>
       </c>
       <c r="G156" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H156" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I156" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J156">
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>48</v>
-      </c>
-      <c r="R156" t="s">
-        <v>34</v>
-      </c>
-      <c r="S156" t="s">
-        <v>43</v>
-      </c>
-      <c r="U156" t="s">
-        <v>34</v>
-      </c>
-      <c r="X156">
+        <v>55</v>
+      </c>
+      <c r="P156" t="s">
+        <v>67</v>
+      </c>
+      <c r="W156" t="s">
+        <v>39</v>
+      </c>
+      <c r="X156" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB156">
         <v>12</v>
       </c>
     </row>
@@ -7293,7 +7710,7 @@
         <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -7305,30 +7722,33 @@
         <v>27</v>
       </c>
       <c r="G157" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H157" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I157" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J157">
         <v>9</v>
       </c>
       <c r="K157" t="s">
-        <v>33</v>
-      </c>
-      <c r="R157" t="s">
-        <v>34</v>
-      </c>
-      <c r="S157" t="s">
-        <v>43</v>
-      </c>
-      <c r="U157" t="s">
-        <v>41</v>
-      </c>
-      <c r="X157">
+        <v>37</v>
+      </c>
+      <c r="P157" t="s">
+        <v>30</v>
+      </c>
+      <c r="W157" t="s">
+        <v>39</v>
+      </c>
+      <c r="X157" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z157" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB157">
         <v>12</v>
       </c>
     </row>
@@ -7340,7 +7760,7 @@
         <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -7352,27 +7772,30 @@
         <v>18</v>
       </c>
       <c r="G158" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H158" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I158" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>48</v>
-      </c>
-      <c r="R158" t="s">
-        <v>34</v>
-      </c>
-      <c r="S158" t="s">
-        <v>43</v>
-      </c>
-      <c r="X158">
+        <v>55</v>
+      </c>
+      <c r="P158" t="s">
+        <v>111</v>
+      </c>
+      <c r="W158" t="s">
+        <v>39</v>
+      </c>
+      <c r="X158" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB158">
         <v>12</v>
       </c>
     </row>
@@ -7384,7 +7807,7 @@
         <v>4</v>
       </c>
       <c r="C159" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -7396,18 +7819,18 @@
         <v>18</v>
       </c>
       <c r="G159" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I159" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J159">
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>48</v>
-      </c>
-      <c r="X159">
+        <v>55</v>
+      </c>
+      <c r="AB159">
         <v>12</v>
       </c>
     </row>
@@ -7419,7 +7842,7 @@
         <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D160">
         <v>2</v>
@@ -7431,30 +7854,33 @@
         <v>18</v>
       </c>
       <c r="G160" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H160" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I160" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J160">
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>48</v>
-      </c>
-      <c r="R160" t="s">
-        <v>99</v>
-      </c>
-      <c r="S160" t="s">
-        <v>53</v>
-      </c>
-      <c r="U160" t="s">
-        <v>34</v>
-      </c>
-      <c r="X160">
+        <v>55</v>
+      </c>
+      <c r="P160" t="s">
+        <v>113</v>
+      </c>
+      <c r="W160" t="s">
+        <v>114</v>
+      </c>
+      <c r="X160" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z160" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB160">
         <v>12</v>
       </c>
     </row>
@@ -7466,7 +7892,7 @@
         <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D161">
         <v>3</v>
@@ -7478,30 +7904,33 @@
         <v>18</v>
       </c>
       <c r="G161" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H161" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I161" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J161">
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>48</v>
-      </c>
-      <c r="R161" t="s">
-        <v>34</v>
-      </c>
-      <c r="S161" t="s">
-        <v>43</v>
-      </c>
-      <c r="U161" t="s">
-        <v>41</v>
-      </c>
-      <c r="X161">
+        <v>55</v>
+      </c>
+      <c r="P161" t="s">
+        <v>67</v>
+      </c>
+      <c r="W161" t="s">
+        <v>39</v>
+      </c>
+      <c r="X161" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z161" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB161">
         <v>12</v>
       </c>
     </row>
